--- a/research/traditional_assets/database/data/estonia/estonia_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07434422067787463</v>
+        <v>0.07423153223651889</v>
       </c>
       <c r="C2">
-        <v>710.3016819763402</v>
+        <v>705.2171011797445</v>
       </c>
       <c r="D2">
-        <v>696.1016819763402</v>
+        <v>698.6321011797445</v>
       </c>
       <c r="E2">
-        <v>-362.2</v>
+        <v>-354.585</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.615</v>
       </c>
       <c r="G2">
         <v>14.2</v>
@@ -1451,28 +1451,28 @@
         <v>26.425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3830345</v>
       </c>
       <c r="N2">
-        <v>26.425</v>
+        <v>26.0419655</v>
       </c>
       <c r="O2">
-        <v>5.285</v>
+        <v>5.208393099999999</v>
       </c>
       <c r="P2">
-        <v>21.14</v>
+        <v>20.8335724</v>
       </c>
       <c r="Q2">
-        <v>68.34</v>
+        <v>68.0335724</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07434422067787463</v>
+        <v>0.07457488104698878</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171842</v>
+        <v>0.5458488604849998</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>68.98856369334877</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07423153223651889</v>
+        <v>0.07411884379516313</v>
       </c>
       <c r="C3">
-        <v>705.2171011797445</v>
+        <v>700.1509843008132</v>
       </c>
       <c r="D3">
-        <v>698.6321011797445</v>
+        <v>701.1809843008132</v>
       </c>
       <c r="E3">
-        <v>-354.585</v>
+        <v>-346.97</v>
       </c>
       <c r="F3">
-        <v>7.615</v>
+        <v>15.23</v>
       </c>
       <c r="G3">
         <v>14.2</v>
@@ -1533,28 +1533,28 @@
         <v>26.425</v>
       </c>
       <c r="M3">
-        <v>0.3830345</v>
+        <v>0.766069</v>
       </c>
       <c r="N3">
-        <v>26.0419655</v>
+        <v>25.658931</v>
       </c>
       <c r="O3">
-        <v>5.208393099999999</v>
+        <v>5.1317862</v>
       </c>
       <c r="P3">
-        <v>20.8335724</v>
+        <v>20.52714479999999</v>
       </c>
       <c r="Q3">
-        <v>68.0335724</v>
+        <v>67.72714479999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07457488104698878</v>
+        <v>0.07481024877057463</v>
       </c>
       <c r="T3">
-        <v>0.5458488604849998</v>
+        <v>0.5503136992276688</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>68.98856369334877</v>
+        <v>34.49428184667438</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07411884379516313</v>
+        <v>0.07400615535380739</v>
       </c>
       <c r="C4">
-        <v>700.1509843008132</v>
+        <v>695.1035341703287</v>
       </c>
       <c r="D4">
-        <v>701.1809843008132</v>
+        <v>703.7485341703286</v>
       </c>
       <c r="E4">
-        <v>-346.97</v>
+        <v>-339.355</v>
       </c>
       <c r="F4">
-        <v>15.23</v>
+        <v>22.845</v>
       </c>
       <c r="G4">
         <v>14.2</v>
@@ -1615,28 +1615,28 @@
         <v>26.425</v>
       </c>
       <c r="M4">
-        <v>0.766069</v>
+        <v>1.1491035</v>
       </c>
       <c r="N4">
-        <v>25.658931</v>
+        <v>25.2758965</v>
       </c>
       <c r="O4">
-        <v>5.1317862</v>
+        <v>5.0551793</v>
       </c>
       <c r="P4">
-        <v>20.52714479999999</v>
+        <v>20.2207172</v>
       </c>
       <c r="Q4">
-        <v>67.72714479999999</v>
+        <v>67.4207172</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07481024877057463</v>
+        <v>0.07505046943691483</v>
       </c>
       <c r="T4">
-        <v>0.5503136992276688</v>
+        <v>0.5548705965011145</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.49428184667438</v>
+        <v>22.99618789778292</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07400615535380739</v>
+        <v>0.07389346691245165</v>
       </c>
       <c r="C5">
-        <v>695.1035341703287</v>
+        <v>690.0749566008558</v>
       </c>
       <c r="D5">
-        <v>703.7485341703286</v>
+        <v>706.3349566008558</v>
       </c>
       <c r="E5">
-        <v>-339.355</v>
+        <v>-331.74</v>
       </c>
       <c r="F5">
-        <v>22.845</v>
+        <v>30.46</v>
       </c>
       <c r="G5">
         <v>14.2</v>
@@ -1697,28 +1697,28 @@
         <v>26.425</v>
       </c>
       <c r="M5">
-        <v>1.1491035</v>
+        <v>1.532138</v>
       </c>
       <c r="N5">
-        <v>25.2758965</v>
+        <v>24.892862</v>
       </c>
       <c r="O5">
-        <v>5.0551793</v>
+        <v>4.9785724</v>
       </c>
       <c r="P5">
-        <v>20.2207172</v>
+        <v>19.9142896</v>
       </c>
       <c r="Q5">
-        <v>67.4207172</v>
+        <v>67.11428960000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07505046943691483</v>
+        <v>0.07529569470047047</v>
       </c>
       <c r="T5">
-        <v>0.5548705965011145</v>
+        <v>0.5595224291344237</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.99618789778292</v>
+        <v>17.24714092333719</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07389346691245165</v>
+        <v>0.07378077847109589</v>
       </c>
       <c r="C6">
-        <v>690.0749566008558</v>
+        <v>685.0654604417365</v>
       </c>
       <c r="D6">
-        <v>706.3349566008558</v>
+        <v>708.9404604417365</v>
       </c>
       <c r="E6">
-        <v>-331.74</v>
+        <v>-324.125</v>
       </c>
       <c r="F6">
-        <v>30.46</v>
+        <v>38.075</v>
       </c>
       <c r="G6">
         <v>14.2</v>
@@ -1779,28 +1779,28 @@
         <v>26.425</v>
       </c>
       <c r="M6">
-        <v>1.532138</v>
+        <v>1.9151725</v>
       </c>
       <c r="N6">
-        <v>24.892862</v>
+        <v>24.5098275</v>
       </c>
       <c r="O6">
-        <v>4.9785724</v>
+        <v>4.901965499999999</v>
       </c>
       <c r="P6">
-        <v>19.9142896</v>
+        <v>19.607862</v>
       </c>
       <c r="Q6">
-        <v>67.11428960000001</v>
+        <v>66.807862</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07529569470047047</v>
+        <v>0.07554608260115357</v>
       </c>
       <c r="T6">
-        <v>0.5595224291344237</v>
+        <v>0.5642721950863288</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.24714092333719</v>
+        <v>13.79771273866975</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07378077847109589</v>
+        <v>0.07374009002974014</v>
       </c>
       <c r="C7">
-        <v>685.0654604417365</v>
+        <v>678.3959599039781</v>
       </c>
       <c r="D7">
-        <v>708.9404604417365</v>
+        <v>709.8859599039781</v>
       </c>
       <c r="E7">
-        <v>-324.125</v>
+        <v>-316.51</v>
       </c>
       <c r="F7">
-        <v>38.075</v>
+        <v>45.69</v>
       </c>
       <c r="G7">
         <v>14.2</v>
@@ -1861,45 +1861,45 @@
         <v>26.425</v>
       </c>
       <c r="M7">
-        <v>1.9151725</v>
+        <v>2.366742</v>
       </c>
       <c r="N7">
-        <v>24.5098275</v>
+        <v>24.058258</v>
       </c>
       <c r="O7">
-        <v>4.901965499999999</v>
+        <v>4.811651599999999</v>
       </c>
       <c r="P7">
-        <v>19.607862</v>
+        <v>19.2466064</v>
       </c>
       <c r="Q7">
-        <v>66.807862</v>
+        <v>66.44660640000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07554608260115357</v>
+        <v>0.07580179790397887</v>
       </c>
       <c r="T7">
-        <v>0.5642721950863288</v>
+        <v>0.5691230198882744</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.79771273866975</v>
+        <v>11.16513756041005</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07374009002974014</v>
+        <v>0.07373460158838439</v>
       </c>
       <c r="C8">
-        <v>678.3959599039781</v>
+        <v>670.9086908770394</v>
       </c>
       <c r="D8">
-        <v>709.8859599039781</v>
+        <v>710.0136908770393</v>
       </c>
       <c r="E8">
-        <v>-316.51</v>
+        <v>-308.895</v>
       </c>
       <c r="F8">
-        <v>45.69</v>
+        <v>53.30499999999999</v>
       </c>
       <c r="G8">
         <v>14.2</v>
@@ -1943,45 +1943,45 @@
         <v>26.425</v>
       </c>
       <c r="M8">
-        <v>2.366742</v>
+        <v>2.8518175</v>
       </c>
       <c r="N8">
-        <v>24.058258</v>
+        <v>23.5731825</v>
       </c>
       <c r="O8">
-        <v>4.8116516</v>
+        <v>4.7146365</v>
       </c>
       <c r="P8">
-        <v>19.2466064</v>
+        <v>18.858546</v>
       </c>
       <c r="Q8">
-        <v>66.44660640000001</v>
+        <v>66.05854600000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07580179790397887</v>
+        <v>0.07606301246062838</v>
       </c>
       <c r="T8">
-        <v>0.5691230198882744</v>
+        <v>0.5740781635031652</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>11.16513756041005</v>
+        <v>9.266020704340303</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07373460158838439</v>
+        <v>0.07364751314702864</v>
       </c>
       <c r="C9">
-        <v>670.9086908770394</v>
+        <v>665.3266449531444</v>
       </c>
       <c r="D9">
-        <v>710.0136908770393</v>
+        <v>712.0466449531443</v>
       </c>
       <c r="E9">
-        <v>-308.895</v>
+        <v>-301.28</v>
       </c>
       <c r="F9">
-        <v>53.30500000000001</v>
+        <v>60.92</v>
       </c>
       <c r="G9">
         <v>14.2</v>
@@ -2025,28 +2025,28 @@
         <v>26.425</v>
       </c>
       <c r="M9">
-        <v>2.8518175</v>
+        <v>3.25922</v>
       </c>
       <c r="N9">
-        <v>23.5731825</v>
+        <v>23.16578</v>
       </c>
       <c r="O9">
-        <v>4.7146365</v>
+        <v>4.633156</v>
       </c>
       <c r="P9">
-        <v>18.858546</v>
+        <v>18.532624</v>
       </c>
       <c r="Q9">
-        <v>66.05854600000001</v>
+        <v>65.732624</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07606301246062838</v>
+        <v>0.07632990559459635</v>
       </c>
       <c r="T9">
-        <v>0.5740781635031652</v>
+        <v>0.5791410276314231</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.266020704340301</v>
+        <v>8.107768116297763</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07364751314702864</v>
+        <v>0.0736180247056729</v>
       </c>
       <c r="C10">
-        <v>665.3266449531444</v>
+        <v>658.4026509979715</v>
       </c>
       <c r="D10">
-        <v>712.0466449531443</v>
+        <v>712.7376509979714</v>
       </c>
       <c r="E10">
-        <v>-301.28</v>
+        <v>-293.665</v>
       </c>
       <c r="F10">
-        <v>60.92</v>
+        <v>68.535</v>
       </c>
       <c r="G10">
         <v>14.2</v>
@@ -2107,45 +2107,45 @@
         <v>26.425</v>
       </c>
       <c r="M10">
-        <v>3.25922</v>
+        <v>3.7214505</v>
       </c>
       <c r="N10">
-        <v>23.16578</v>
+        <v>22.7035495</v>
       </c>
       <c r="O10">
-        <v>4.633156</v>
+        <v>4.5407099</v>
       </c>
       <c r="P10">
-        <v>18.532624</v>
+        <v>18.1628396</v>
       </c>
       <c r="Q10">
-        <v>65.732624</v>
+        <v>65.3628396</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07632990559459635</v>
+        <v>0.07660266451172845</v>
       </c>
       <c r="T10">
-        <v>0.5791410276314231</v>
+        <v>0.5843151634987636</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.107768116297763</v>
+        <v>7.100725913188956</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0736180247056729</v>
+        <v>0.07353733626431716</v>
       </c>
       <c r="C11">
-        <v>658.4026509979715</v>
+        <v>652.6853065223635</v>
       </c>
       <c r="D11">
-        <v>712.7376509979714</v>
+        <v>714.6353065223634</v>
       </c>
       <c r="E11">
-        <v>-293.665</v>
+        <v>-286.05</v>
       </c>
       <c r="F11">
-        <v>68.535</v>
+        <v>76.14999999999999</v>
       </c>
       <c r="G11">
         <v>14.2</v>
@@ -2189,28 +2189,28 @@
         <v>26.425</v>
       </c>
       <c r="M11">
-        <v>3.7214505</v>
+        <v>4.134944999999999</v>
       </c>
       <c r="N11">
-        <v>22.7035495</v>
+        <v>22.290055</v>
       </c>
       <c r="O11">
-        <v>4.5407099</v>
+        <v>4.458011</v>
       </c>
       <c r="P11">
-        <v>18.1628396</v>
+        <v>17.832044</v>
       </c>
       <c r="Q11">
-        <v>65.3628396</v>
+        <v>65.032044</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07660266451172845</v>
+        <v>0.07688148473813017</v>
       </c>
       <c r="T11">
-        <v>0.5843151634987636</v>
+        <v>0.589604280163156</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.100725913188956</v>
+        <v>6.390653321870062</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07353733626431716</v>
+        <v>0.07354464782296138</v>
       </c>
       <c r="C12">
-        <v>652.6853065223635</v>
+        <v>644.8979347995712</v>
       </c>
       <c r="D12">
-        <v>714.6353065223634</v>
+        <v>714.4629347995711</v>
       </c>
       <c r="E12">
-        <v>-286.05</v>
+        <v>-278.435</v>
       </c>
       <c r="F12">
-        <v>76.15000000000001</v>
+        <v>83.765</v>
       </c>
       <c r="G12">
         <v>14.2</v>
@@ -2271,45 +2271,45 @@
         <v>26.425</v>
       </c>
       <c r="M12">
-        <v>4.134945</v>
+        <v>4.6322045</v>
       </c>
       <c r="N12">
-        <v>22.290055</v>
+        <v>21.7927955</v>
       </c>
       <c r="O12">
-        <v>4.458010999999999</v>
+        <v>4.3585591</v>
       </c>
       <c r="P12">
-        <v>17.832044</v>
+        <v>17.4342364</v>
       </c>
       <c r="Q12">
-        <v>65.032044</v>
+        <v>64.63423639999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07688148473813017</v>
+        <v>0.07716657058759707</v>
       </c>
       <c r="T12">
-        <v>0.5896042801631561</v>
+        <v>0.5950122533818046</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.39065332187006</v>
+        <v>5.704627246055306</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07354464782296138</v>
+        <v>0.07347195938160565</v>
       </c>
       <c r="C13">
-        <v>644.8979347995712</v>
+        <v>639.0002867393177</v>
       </c>
       <c r="D13">
-        <v>714.4629347995711</v>
+        <v>716.1802867393177</v>
       </c>
       <c r="E13">
-        <v>-278.435</v>
+        <v>-270.82</v>
       </c>
       <c r="F13">
-        <v>83.765</v>
+        <v>91.38</v>
       </c>
       <c r="G13">
         <v>14.2</v>
@@ -2353,28 +2353,28 @@
         <v>26.425</v>
       </c>
       <c r="M13">
-        <v>4.6322045</v>
+        <v>5.053314</v>
       </c>
       <c r="N13">
-        <v>21.7927955</v>
+        <v>21.371686</v>
       </c>
       <c r="O13">
-        <v>4.3585591</v>
+        <v>4.2743372</v>
       </c>
       <c r="P13">
-        <v>17.4342364</v>
+        <v>17.0973488</v>
       </c>
       <c r="Q13">
-        <v>64.63423639999999</v>
+        <v>64.29734880000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07716657058759707</v>
+        <v>0.07745813566091551</v>
       </c>
       <c r="T13">
-        <v>0.5950122533818046</v>
+        <v>0.6005431350826952</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.704627246055306</v>
+        <v>5.229241642217364</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07347195938160565</v>
+        <v>0.07339927094024989</v>
       </c>
       <c r="C14">
-        <v>639.0002867393177</v>
+        <v>633.1109145568981</v>
       </c>
       <c r="D14">
-        <v>716.1802867393177</v>
+        <v>717.9059145568981</v>
       </c>
       <c r="E14">
-        <v>-270.82</v>
+        <v>-263.205</v>
       </c>
       <c r="F14">
-        <v>91.38</v>
+        <v>98.995</v>
       </c>
       <c r="G14">
         <v>14.2</v>
@@ -2435,28 +2435,28 @@
         <v>26.425</v>
       </c>
       <c r="M14">
-        <v>5.053314</v>
+        <v>5.4744235</v>
       </c>
       <c r="N14">
-        <v>21.371686</v>
+        <v>20.9505765</v>
       </c>
       <c r="O14">
-        <v>4.2743372</v>
+        <v>4.1901153</v>
       </c>
       <c r="P14">
-        <v>17.0973488</v>
+        <v>16.7604612</v>
       </c>
       <c r="Q14">
-        <v>64.29734880000001</v>
+        <v>63.9604612</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07745813566091551</v>
+        <v>0.07775640337959758</v>
       </c>
       <c r="T14">
-        <v>0.6005431350826952</v>
+        <v>0.6062011634893533</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.229241642217364</v>
+        <v>4.826992285123721</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07339927094024989</v>
+        <v>0.07360658249889415</v>
       </c>
       <c r="C15">
-        <v>633.1109145568981</v>
+        <v>620.5961388528159</v>
       </c>
       <c r="D15">
-        <v>717.9059145568981</v>
+        <v>713.0061388528159</v>
       </c>
       <c r="E15">
-        <v>-263.205</v>
+        <v>-255.59</v>
       </c>
       <c r="F15">
-        <v>98.995</v>
+        <v>106.61</v>
       </c>
       <c r="G15">
         <v>14.2</v>
@@ -2517,45 +2517,45 @@
         <v>26.425</v>
       </c>
       <c r="M15">
-        <v>5.4744235</v>
+        <v>6.162058000000001</v>
       </c>
       <c r="N15">
-        <v>20.9505765</v>
+        <v>20.262942</v>
       </c>
       <c r="O15">
-        <v>4.1901153</v>
+        <v>4.052588399999999</v>
       </c>
       <c r="P15">
-        <v>16.7604612</v>
+        <v>16.2103536</v>
       </c>
       <c r="Q15">
-        <v>63.9604612</v>
+        <v>63.4103536</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07775640337959758</v>
+        <v>0.07806160755685367</v>
       </c>
       <c r="T15">
-        <v>0.6062011634893533</v>
+        <v>0.6119907739519803</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.826992285123721</v>
+        <v>4.288340031852993</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07360658249889415</v>
+        <v>0.07355389405753839</v>
       </c>
       <c r="C16">
-        <v>620.5961388528159</v>
+        <v>614.220071666168</v>
       </c>
       <c r="D16">
-        <v>713.0061388528159</v>
+        <v>714.245071666168</v>
       </c>
       <c r="E16">
-        <v>-255.59</v>
+        <v>-247.975</v>
       </c>
       <c r="F16">
-        <v>106.61</v>
+        <v>114.225</v>
       </c>
       <c r="G16">
         <v>14.2</v>
@@ -2599,28 +2599,28 @@
         <v>26.425</v>
       </c>
       <c r="M16">
-        <v>6.162058000000001</v>
+        <v>6.602205000000001</v>
       </c>
       <c r="N16">
-        <v>20.262942</v>
+        <v>19.822795</v>
       </c>
       <c r="O16">
-        <v>4.052588399999999</v>
+        <v>3.964559</v>
       </c>
       <c r="P16">
-        <v>16.2103536</v>
+        <v>15.858236</v>
       </c>
       <c r="Q16">
-        <v>63.4103536</v>
+        <v>63.058236</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07806160755685367</v>
+        <v>0.0783739930088687</v>
       </c>
       <c r="T16">
-        <v>0.6119907739519803</v>
+        <v>0.6179166105431395</v>
       </c>
       <c r="U16">
         <v>0.0578</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.288340031852993</v>
+        <v>4.002450696396127</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07355389405753839</v>
+        <v>0.07394920561618265</v>
       </c>
       <c r="C17">
-        <v>614.220071666168</v>
+        <v>597.413271371998</v>
       </c>
       <c r="D17">
-        <v>714.245071666168</v>
+        <v>705.053271371998</v>
       </c>
       <c r="E17">
-        <v>-247.975</v>
+        <v>-240.36</v>
       </c>
       <c r="F17">
-        <v>114.225</v>
+        <v>121.84</v>
       </c>
       <c r="G17">
         <v>14.2</v>
@@ -2681,45 +2681,45 @@
         <v>26.425</v>
       </c>
       <c r="M17">
-        <v>6.602205000000001</v>
+        <v>7.468792000000001</v>
       </c>
       <c r="N17">
-        <v>19.822795</v>
+        <v>18.956208</v>
       </c>
       <c r="O17">
-        <v>3.964559</v>
+        <v>3.791241599999999</v>
       </c>
       <c r="P17">
-        <v>15.858236</v>
+        <v>15.1649664</v>
       </c>
       <c r="Q17">
-        <v>63.058236</v>
+        <v>62.3649664</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0783739930088687</v>
+        <v>0.07869381620974125</v>
       </c>
       <c r="T17">
-        <v>0.6179166105431395</v>
+        <v>0.6239835384817074</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.002450696396128</v>
+        <v>3.538055417797148</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07394920561618265</v>
+        <v>0.0743053171748269</v>
       </c>
       <c r="C18">
-        <v>597.413271371998</v>
+        <v>581.7181858962831</v>
       </c>
       <c r="D18">
-        <v>705.053271371998</v>
+        <v>696.9731858962831</v>
       </c>
       <c r="E18">
-        <v>-240.36</v>
+        <v>-232.745</v>
       </c>
       <c r="F18">
-        <v>121.84</v>
+        <v>129.455</v>
       </c>
       <c r="G18">
         <v>14.2</v>
@@ -2763,45 +2763,45 @@
         <v>26.425</v>
       </c>
       <c r="M18">
-        <v>7.468792000000001</v>
+        <v>8.298065500000002</v>
       </c>
       <c r="N18">
-        <v>18.956208</v>
+        <v>18.1269345</v>
       </c>
       <c r="O18">
-        <v>3.791241599999999</v>
+        <v>3.6253869</v>
       </c>
       <c r="P18">
-        <v>15.1649664</v>
+        <v>14.5015476</v>
       </c>
       <c r="Q18">
-        <v>62.3649664</v>
+        <v>61.7015476</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07869381620974125</v>
+        <v>0.07902134599376734</v>
       </c>
       <c r="T18">
-        <v>0.6239835384817074</v>
+        <v>0.6301966574549396</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.538055417797148</v>
+        <v>3.184477153138884</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0743053171748269</v>
+        <v>0.07430302873347115</v>
       </c>
       <c r="C19">
-        <v>581.7181858962831</v>
+        <v>574.1545187957679</v>
       </c>
       <c r="D19">
-        <v>696.9731858962831</v>
+        <v>697.0245187957679</v>
       </c>
       <c r="E19">
-        <v>-232.745</v>
+        <v>-225.13</v>
       </c>
       <c r="F19">
-        <v>129.455</v>
+        <v>137.07</v>
       </c>
       <c r="G19">
         <v>14.2</v>
@@ -2845,28 +2845,28 @@
         <v>26.425</v>
       </c>
       <c r="M19">
-        <v>8.298065500000002</v>
+        <v>8.786187000000002</v>
       </c>
       <c r="N19">
-        <v>18.1269345</v>
+        <v>17.638813</v>
       </c>
       <c r="O19">
-        <v>3.6253869</v>
+        <v>3.527762599999999</v>
       </c>
       <c r="P19">
-        <v>14.5015476</v>
+        <v>14.1110504</v>
       </c>
       <c r="Q19">
-        <v>61.7015476</v>
+        <v>61.3110504</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07902134599376734</v>
+        <v>0.07935686430911117</v>
       </c>
       <c r="T19">
-        <v>0.6301966574549396</v>
+        <v>0.6365613159153239</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.184477153138884</v>
+        <v>3.007561755742279</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07430302873347115</v>
+        <v>0.07548634029211541</v>
       </c>
       <c r="C20">
-        <v>574.1545187957679</v>
+        <v>540.9681055036515</v>
       </c>
       <c r="D20">
-        <v>697.0245187957679</v>
+        <v>671.4531055036514</v>
       </c>
       <c r="E20">
-        <v>-225.13</v>
+        <v>-217.515</v>
       </c>
       <c r="F20">
-        <v>137.07</v>
+        <v>144.685</v>
       </c>
       <c r="G20">
         <v>14.2</v>
@@ -2927,45 +2927,45 @@
         <v>26.425</v>
       </c>
       <c r="M20">
-        <v>8.786187</v>
+        <v>10.4028515</v>
       </c>
       <c r="N20">
-        <v>17.638813</v>
+        <v>16.0221485</v>
       </c>
       <c r="O20">
-        <v>3.5277626</v>
+        <v>3.204429699999999</v>
       </c>
       <c r="P20">
-        <v>14.1110504</v>
+        <v>12.8177188</v>
       </c>
       <c r="Q20">
-        <v>61.3110504</v>
+        <v>60.0177188</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07935686430911115</v>
+        <v>0.07970066702730297</v>
       </c>
       <c r="T20">
-        <v>0.6365613159153238</v>
+        <v>0.6430831264364583</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.00756175574228</v>
+        <v>2.540168914263555</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07548634029211541</v>
+        <v>0.07617045185075966</v>
       </c>
       <c r="C21">
-        <v>540.9681055036515</v>
+        <v>519.4075681343907</v>
       </c>
       <c r="D21">
-        <v>671.4531055036514</v>
+        <v>657.5075681343906</v>
       </c>
       <c r="E21">
-        <v>-217.515</v>
+        <v>-209.9</v>
       </c>
       <c r="F21">
-        <v>144.685</v>
+        <v>152.3</v>
       </c>
       <c r="G21">
         <v>14.2</v>
@@ -3009,45 +3009,45 @@
         <v>26.425</v>
       </c>
       <c r="M21">
-        <v>10.4028515</v>
+        <v>11.54434</v>
       </c>
       <c r="N21">
-        <v>16.0221485</v>
+        <v>14.88066</v>
       </c>
       <c r="O21">
-        <v>3.204429699999999</v>
+        <v>2.976131999999999</v>
       </c>
       <c r="P21">
-        <v>12.8177188</v>
+        <v>11.904528</v>
       </c>
       <c r="Q21">
-        <v>60.0177188</v>
+        <v>59.104528</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07970066702730297</v>
+        <v>0.08005306481344956</v>
       </c>
       <c r="T21">
-        <v>0.6430831264364583</v>
+        <v>0.6497679822206209</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.540168914263555</v>
+        <v>2.289000497213352</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07617045185075966</v>
+        <v>0.07626176340940392</v>
       </c>
       <c r="C22">
-        <v>519.4075681343907</v>
+        <v>509.9748904206929</v>
       </c>
       <c r="D22">
-        <v>657.5075681343906</v>
+        <v>655.6898904206929</v>
       </c>
       <c r="E22">
-        <v>-209.9</v>
+        <v>-202.285</v>
       </c>
       <c r="F22">
-        <v>152.3</v>
+        <v>159.915</v>
       </c>
       <c r="G22">
         <v>14.2</v>
@@ -3091,28 +3091,28 @@
         <v>26.425</v>
       </c>
       <c r="M22">
-        <v>11.54434</v>
+        <v>12.121557</v>
       </c>
       <c r="N22">
-        <v>14.88066</v>
+        <v>14.30344299999999</v>
       </c>
       <c r="O22">
-        <v>2.976131999999999</v>
+        <v>2.860688599999999</v>
       </c>
       <c r="P22">
-        <v>11.904528</v>
+        <v>11.44275439999999</v>
       </c>
       <c r="Q22">
-        <v>59.104528</v>
+        <v>58.6427544</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08005306481344956</v>
+        <v>0.08041438406253659</v>
       </c>
       <c r="T22">
-        <v>0.6497679822206209</v>
+        <v>0.6566220748600791</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.289000497213352</v>
+        <v>2.180000473536526</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07626176340940392</v>
+        <v>0.07635307496804816</v>
       </c>
       <c r="C23">
-        <v>509.974890420693</v>
+        <v>500.5522349298418</v>
       </c>
       <c r="D23">
-        <v>655.6898904206929</v>
+        <v>653.8822349298417</v>
       </c>
       <c r="E23">
-        <v>-202.285</v>
+        <v>-194.67</v>
       </c>
       <c r="F23">
-        <v>159.915</v>
+        <v>167.53</v>
       </c>
       <c r="G23">
         <v>14.2</v>
@@ -3173,28 +3173,28 @@
         <v>26.425</v>
       </c>
       <c r="M23">
-        <v>12.121557</v>
+        <v>12.698774</v>
       </c>
       <c r="N23">
-        <v>14.303443</v>
+        <v>13.726226</v>
       </c>
       <c r="O23">
-        <v>2.8606886</v>
+        <v>2.745245199999999</v>
       </c>
       <c r="P23">
-        <v>11.4427544</v>
+        <v>10.9809808</v>
       </c>
       <c r="Q23">
-        <v>58.6427544</v>
+        <v>58.1809808</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08041438406253659</v>
+        <v>0.08078496790775405</v>
       </c>
       <c r="T23">
-        <v>0.6566220748600791</v>
+        <v>0.6636519134646514</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.180000473536526</v>
+        <v>2.080909542921229</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07635307496804816</v>
+        <v>0.07905718652669241</v>
       </c>
       <c r="C24">
-        <v>500.5522349298418</v>
+        <v>443.5821571176936</v>
       </c>
       <c r="D24">
-        <v>653.8822349298417</v>
+        <v>604.5271571176935</v>
       </c>
       <c r="E24">
-        <v>-194.67</v>
+        <v>-187.055</v>
       </c>
       <c r="F24">
-        <v>167.53</v>
+        <v>175.145</v>
       </c>
       <c r="G24">
         <v>14.2</v>
@@ -3255,45 +3255,45 @@
         <v>26.425</v>
       </c>
       <c r="M24">
-        <v>12.698774</v>
+        <v>15.76305</v>
       </c>
       <c r="N24">
-        <v>13.726226</v>
+        <v>10.66195</v>
       </c>
       <c r="O24">
-        <v>2.745245199999999</v>
+        <v>2.13239</v>
       </c>
       <c r="P24">
-        <v>10.9809808</v>
+        <v>8.529559999999998</v>
       </c>
       <c r="Q24">
-        <v>58.1809808</v>
+        <v>55.72956</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08078496790775405</v>
+        <v>0.08116517730739274</v>
       </c>
       <c r="T24">
-        <v>0.6636519134646514</v>
+        <v>0.6708643452797322</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.080909542921229</v>
+        <v>1.676388769939827</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07905718652669241</v>
+        <v>0.07926209808533666</v>
       </c>
       <c r="C25">
-        <v>443.5821571176936</v>
+        <v>432.5291006299876</v>
       </c>
       <c r="D25">
-        <v>604.5271571176935</v>
+        <v>601.0891006299876</v>
       </c>
       <c r="E25">
-        <v>-187.055</v>
+        <v>-179.44</v>
       </c>
       <c r="F25">
-        <v>175.145</v>
+        <v>182.76</v>
       </c>
       <c r="G25">
         <v>14.2</v>
@@ -3337,28 +3337,28 @@
         <v>26.425</v>
       </c>
       <c r="M25">
-        <v>15.76305</v>
+        <v>16.4484</v>
       </c>
       <c r="N25">
-        <v>10.66195</v>
+        <v>9.976599999999998</v>
       </c>
       <c r="O25">
-        <v>2.13239</v>
+        <v>1.99532</v>
       </c>
       <c r="P25">
-        <v>8.529559999999998</v>
+        <v>7.981279999999998</v>
       </c>
       <c r="Q25">
-        <v>55.72956</v>
+        <v>55.18128</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08116517730739274</v>
+        <v>0.08155539221754823</v>
       </c>
       <c r="T25">
-        <v>0.6708643452797322</v>
+        <v>0.6782665779320518</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.676388769939827</v>
+        <v>1.606539237859001</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07926209808533666</v>
+        <v>0.0794670096439809</v>
       </c>
       <c r="C26">
-        <v>432.5291006299876</v>
+        <v>421.5149287105041</v>
       </c>
       <c r="D26">
-        <v>601.0891006299876</v>
+        <v>597.6899287105041</v>
       </c>
       <c r="E26">
-        <v>-179.44</v>
+        <v>-171.825</v>
       </c>
       <c r="F26">
-        <v>182.76</v>
+        <v>190.375</v>
       </c>
       <c r="G26">
         <v>14.2</v>
@@ -3419,28 +3419,28 @@
         <v>26.425</v>
       </c>
       <c r="M26">
-        <v>16.4484</v>
+        <v>17.13375</v>
       </c>
       <c r="N26">
-        <v>9.976599999999998</v>
+        <v>9.291249999999998</v>
       </c>
       <c r="O26">
-        <v>1.99532</v>
+        <v>1.85825</v>
       </c>
       <c r="P26">
-        <v>7.981279999999998</v>
+        <v>7.432999999999998</v>
       </c>
       <c r="Q26">
-        <v>55.18128</v>
+        <v>54.633</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08155539221754823</v>
+        <v>0.08195601285864121</v>
       </c>
       <c r="T26">
-        <v>0.6782665779320517</v>
+        <v>0.6858662034551</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.606539237859001</v>
+        <v>1.542277668344641</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0794670096439809</v>
+        <v>0.09231448878951283</v>
       </c>
       <c r="C27">
-        <v>421.5149287105041</v>
+        <v>257.4539231052047</v>
       </c>
       <c r="D27">
-        <v>597.6899287105041</v>
+        <v>441.2439231052047</v>
       </c>
       <c r="E27">
-        <v>-171.825</v>
+        <v>-164.21</v>
       </c>
       <c r="F27">
-        <v>190.375</v>
+        <v>197.99</v>
       </c>
       <c r="G27">
         <v>14.2</v>
@@ -3501,45 +3501,45 @@
         <v>26.425</v>
       </c>
       <c r="M27">
-        <v>17.13375</v>
+        <v>29.064932</v>
       </c>
       <c r="N27">
-        <v>9.291249999999998</v>
+        <v>-2.639932000000005</v>
       </c>
       <c r="O27">
-        <v>1.85825</v>
+        <v>-0.5279864000000011</v>
       </c>
       <c r="P27">
-        <v>7.432999999999998</v>
+        <v>-2.111945600000004</v>
       </c>
       <c r="Q27">
-        <v>54.633</v>
+        <v>45.0880544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08195601285864121</v>
+        <v>0.0825496463473834</v>
       </c>
       <c r="T27">
-        <v>0.6858662034551</v>
+        <v>0.697127211375394</v>
       </c>
       <c r="U27">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2</v>
+        <v>0.1818342461630393</v>
       </c>
       <c r="W27">
-        <v>0.07199999999999999</v>
+        <v>0.1201067326632658</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y27">
-        <v>1.542277668344641</v>
+        <v>0.9091712308151967</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09231448878951283</v>
+        <v>0.09332448878951284</v>
       </c>
       <c r="C28">
-        <v>257.4539231052047</v>
+        <v>240.9423089872868</v>
       </c>
       <c r="D28">
-        <v>441.2439231052047</v>
+        <v>432.3473089872869</v>
       </c>
       <c r="E28">
-        <v>-164.21</v>
+        <v>-156.595</v>
       </c>
       <c r="F28">
-        <v>197.99</v>
+        <v>205.605</v>
       </c>
       <c r="G28">
         <v>14.2</v>
@@ -3583,37 +3583,37 @@
         <v>26.425</v>
       </c>
       <c r="M28">
-        <v>29.064932</v>
+        <v>30.182814</v>
       </c>
       <c r="N28">
-        <v>-2.639932000000005</v>
+        <v>-3.757814000000007</v>
       </c>
       <c r="O28">
-        <v>-0.5279864000000011</v>
+        <v>-0.7515628000000014</v>
       </c>
       <c r="P28">
-        <v>-2.111945600000004</v>
+        <v>-3.006251200000006</v>
       </c>
       <c r="Q28">
-        <v>45.0880544</v>
+        <v>44.19374879999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0825496463473834</v>
+        <v>0.08305306616036126</v>
       </c>
       <c r="T28">
-        <v>0.697127211375394</v>
+        <v>0.7066768992024542</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.1818342461630393</v>
+        <v>0.1750996444532971</v>
       </c>
       <c r="W28">
-        <v>0.1201067326632658</v>
+        <v>0.121095372194256</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.9091712308151967</v>
+        <v>0.8754982222664857</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09332448878951284</v>
+        <v>0.09433448878951284</v>
       </c>
       <c r="C29">
-        <v>240.9423089872868</v>
+        <v>224.7823616765908</v>
       </c>
       <c r="D29">
-        <v>432.3473089872869</v>
+        <v>423.8023616765909</v>
       </c>
       <c r="E29">
-        <v>-156.595</v>
+        <v>-148.98</v>
       </c>
       <c r="F29">
-        <v>205.605</v>
+        <v>213.22</v>
       </c>
       <c r="G29">
         <v>14.2</v>
@@ -3665,37 +3665,37 @@
         <v>26.425</v>
       </c>
       <c r="M29">
-        <v>30.182814</v>
+        <v>31.30069600000001</v>
       </c>
       <c r="N29">
-        <v>-3.757814000000007</v>
+        <v>-4.875696000000008</v>
       </c>
       <c r="O29">
-        <v>-0.7515628000000014</v>
+        <v>-0.9751392000000018</v>
       </c>
       <c r="P29">
-        <v>-3.006251200000006</v>
+        <v>-3.900556800000007</v>
       </c>
       <c r="Q29">
-        <v>44.19374879999999</v>
+        <v>43.2994432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08305306616036126</v>
+        <v>0.08357046985703295</v>
       </c>
       <c r="T29">
-        <v>0.7066768992024542</v>
+        <v>0.7164918561358217</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.1750996444532971</v>
+        <v>0.1688460857228222</v>
       </c>
       <c r="W29">
-        <v>0.121095372194256</v>
+        <v>0.1220133946158897</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.8754982222664857</v>
+        <v>0.8442304286141111</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09433448878951284</v>
+        <v>0.09534448878951285</v>
       </c>
       <c r="C30">
-        <v>224.7823616765908</v>
+        <v>208.9536341752678</v>
       </c>
       <c r="D30">
-        <v>423.8023616765909</v>
+        <v>415.5886341752678</v>
       </c>
       <c r="E30">
-        <v>-148.98</v>
+        <v>-141.365</v>
       </c>
       <c r="F30">
-        <v>213.22</v>
+        <v>220.835</v>
       </c>
       <c r="G30">
         <v>14.2</v>
@@ -3747,37 +3747,37 @@
         <v>26.425</v>
       </c>
       <c r="M30">
-        <v>31.30069600000001</v>
+        <v>32.41857800000001</v>
       </c>
       <c r="N30">
-        <v>-4.875696000000008</v>
+        <v>-5.993578000000014</v>
       </c>
       <c r="O30">
-        <v>-0.9751392000000018</v>
+        <v>-1.198715600000003</v>
       </c>
       <c r="P30">
-        <v>-3.900556800000007</v>
+        <v>-4.794862400000011</v>
       </c>
       <c r="Q30">
-        <v>43.2994432</v>
+        <v>42.40513759999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08357046985703295</v>
+        <v>0.08410244830572355</v>
       </c>
       <c r="T30">
-        <v>0.7164918561358217</v>
+        <v>0.726583290729284</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1688460857228222</v>
+        <v>0.1630238069047938</v>
       </c>
       <c r="W30">
-        <v>0.1220133946158897</v>
+        <v>0.1228681051463763</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8442304286141111</v>
+        <v>0.8151190345239692</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09534448878951284</v>
+        <v>0.1129173973978982</v>
       </c>
       <c r="C31">
-        <v>208.953634175268</v>
+        <v>96.53808559454939</v>
       </c>
       <c r="D31">
-        <v>415.588634175268</v>
+        <v>310.7880855945494</v>
       </c>
       <c r="E31">
-        <v>-141.365</v>
+        <v>-133.75</v>
       </c>
       <c r="F31">
-        <v>220.835</v>
+        <v>228.45</v>
       </c>
       <c r="G31">
         <v>14.2</v>
@@ -3829,45 +3829,45 @@
         <v>26.425</v>
       </c>
       <c r="M31">
-        <v>32.418578</v>
+        <v>45.87276</v>
       </c>
       <c r="N31">
-        <v>-5.993577999999999</v>
+        <v>-19.44776</v>
       </c>
       <c r="O31">
-        <v>-1.1987156</v>
+        <v>-3.889552000000001</v>
       </c>
       <c r="P31">
-        <v>-4.7948624</v>
+        <v>-15.558208</v>
       </c>
       <c r="Q31">
-        <v>42.4051376</v>
+        <v>31.641792</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08410244830572355</v>
+        <v>0.08516806700778445</v>
       </c>
       <c r="T31">
-        <v>0.726583290729284</v>
+        <v>0.7467976837369077</v>
       </c>
       <c r="U31">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1630238069047939</v>
+        <v>0.1152099851851077</v>
       </c>
       <c r="W31">
-        <v>0.1228681051463763</v>
+        <v>0.1776658349748304</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.8151190345239696</v>
+        <v>0.5760499259255383</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1129173973978982</v>
+        <v>0.1144673973978982</v>
       </c>
       <c r="C32">
-        <v>96.53808559454939</v>
+        <v>82.16072576711645</v>
       </c>
       <c r="D32">
-        <v>310.7880855945494</v>
+        <v>304.0257257671165</v>
       </c>
       <c r="E32">
-        <v>-133.75</v>
+        <v>-126.135</v>
       </c>
       <c r="F32">
-        <v>228.45</v>
+        <v>236.065</v>
       </c>
       <c r="G32">
         <v>14.2</v>
@@ -3911,37 +3911,37 @@
         <v>26.425</v>
       </c>
       <c r="M32">
-        <v>45.87276</v>
+        <v>47.401852</v>
       </c>
       <c r="N32">
-        <v>-19.44776</v>
+        <v>-20.976852</v>
       </c>
       <c r="O32">
-        <v>-3.889552000000001</v>
+        <v>-4.195370400000001</v>
       </c>
       <c r="P32">
-        <v>-15.558208</v>
+        <v>-16.7814816</v>
       </c>
       <c r="Q32">
-        <v>31.641792</v>
+        <v>30.4185184</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08516806700778445</v>
+        <v>0.08573861870354946</v>
       </c>
       <c r="T32">
-        <v>0.7467976837369077</v>
+        <v>0.7576208385736745</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1152099851851077</v>
+        <v>0.1114935340501042</v>
       </c>
       <c r="W32">
-        <v>0.1776658349748304</v>
+        <v>0.1784120983627391</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5760499259255383</v>
+        <v>0.557467670250521</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1144673973978982</v>
+        <v>0.1160173973978982</v>
       </c>
       <c r="C33">
-        <v>82.16072576711645</v>
+        <v>68.07138008732488</v>
       </c>
       <c r="D33">
-        <v>304.0257257671165</v>
+        <v>297.5513800873249</v>
       </c>
       <c r="E33">
-        <v>-126.135</v>
+        <v>-118.52</v>
       </c>
       <c r="F33">
-        <v>236.065</v>
+        <v>243.68</v>
       </c>
       <c r="G33">
         <v>14.2</v>
@@ -3993,37 +3993,37 @@
         <v>26.425</v>
       </c>
       <c r="M33">
-        <v>47.401852</v>
+        <v>48.930944</v>
       </c>
       <c r="N33">
-        <v>-20.976852</v>
+        <v>-22.50594400000001</v>
       </c>
       <c r="O33">
-        <v>-4.195370400000001</v>
+        <v>-4.501188800000001</v>
       </c>
       <c r="P33">
-        <v>-16.7814816</v>
+        <v>-18.00475520000001</v>
       </c>
       <c r="Q33">
-        <v>30.4185184</v>
+        <v>29.1952448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08573861870354946</v>
+        <v>0.08632595133154283</v>
       </c>
       <c r="T33">
-        <v>0.7576208385736745</v>
+        <v>0.7687623214938756</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1114935340501042</v>
+        <v>0.1080093611110384</v>
       </c>
       <c r="W33">
-        <v>0.1784120983627391</v>
+        <v>0.1791117202889035</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.557467670250521</v>
+        <v>0.5400468055551921</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1160173973978982</v>
+        <v>0.1175673973978983</v>
       </c>
       <c r="C34">
-        <v>68.07138008732488</v>
+        <v>54.25203210374059</v>
       </c>
       <c r="D34">
-        <v>297.5513800873249</v>
+        <v>291.3470321037406</v>
       </c>
       <c r="E34">
-        <v>-118.52</v>
+        <v>-110.905</v>
       </c>
       <c r="F34">
-        <v>243.68</v>
+        <v>251.295</v>
       </c>
       <c r="G34">
         <v>14.2</v>
@@ -4075,37 +4075,37 @@
         <v>26.425</v>
       </c>
       <c r="M34">
-        <v>48.930944</v>
+        <v>50.460036</v>
       </c>
       <c r="N34">
-        <v>-22.50594400000001</v>
+        <v>-24.03503600000001</v>
       </c>
       <c r="O34">
-        <v>-4.501188800000001</v>
+        <v>-4.807007200000001</v>
       </c>
       <c r="P34">
-        <v>-18.00475520000001</v>
+        <v>-19.2280288</v>
       </c>
       <c r="Q34">
-        <v>29.1952448</v>
+        <v>27.9719712</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08632595133154283</v>
+        <v>0.08693081627678975</v>
       </c>
       <c r="T34">
-        <v>0.7687623214938756</v>
+        <v>0.7802363859937843</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1080093611110384</v>
+        <v>0.1047363501682797</v>
       </c>
       <c r="W34">
-        <v>0.1791117202889035</v>
+        <v>0.1797689408862095</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5400468055551921</v>
+        <v>0.5236817508413985</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1175673973978983</v>
+        <v>0.1191173973978982</v>
       </c>
       <c r="C35">
-        <v>54.25203210374059</v>
+        <v>40.68613734157145</v>
       </c>
       <c r="D35">
-        <v>291.3470321037406</v>
+        <v>285.3961373415715</v>
       </c>
       <c r="E35">
-        <v>-110.905</v>
+        <v>-103.29</v>
       </c>
       <c r="F35">
-        <v>251.295</v>
+        <v>258.91</v>
       </c>
       <c r="G35">
         <v>14.2</v>
@@ -4157,37 +4157,37 @@
         <v>26.425</v>
       </c>
       <c r="M35">
-        <v>50.460036</v>
+        <v>51.98912800000001</v>
       </c>
       <c r="N35">
-        <v>-24.03503600000001</v>
+        <v>-25.56412800000001</v>
       </c>
       <c r="O35">
-        <v>-4.807007200000001</v>
+        <v>-5.112825600000003</v>
       </c>
       <c r="P35">
-        <v>-19.2280288</v>
+        <v>-20.45130240000001</v>
       </c>
       <c r="Q35">
-        <v>27.9719712</v>
+        <v>26.74869759999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08693081627678975</v>
+        <v>0.0875540104628017</v>
       </c>
       <c r="T35">
-        <v>0.7802363859937843</v>
+        <v>0.7920581494179324</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1047363501682797</v>
+        <v>0.1016558692809773</v>
       </c>
       <c r="W35">
-        <v>0.1797689408862095</v>
+        <v>0.1803875014483798</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5236817508413985</v>
+        <v>0.5082793464048867</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1191173973978982</v>
+        <v>0.1330638354048316</v>
       </c>
       <c r="C36">
-        <v>40.68613734157145</v>
+        <v>-11.2366014197417</v>
       </c>
       <c r="D36">
-        <v>285.3961373415715</v>
+        <v>241.0883985802583</v>
       </c>
       <c r="E36">
-        <v>-103.29</v>
+        <v>-95.67499999999995</v>
       </c>
       <c r="F36">
-        <v>258.91</v>
+        <v>266.525</v>
       </c>
       <c r="G36">
         <v>14.2</v>
@@ -4239,45 +4239,45 @@
         <v>26.425</v>
       </c>
       <c r="M36">
-        <v>51.98912800000001</v>
+        <v>62.84659500000001</v>
       </c>
       <c r="N36">
-        <v>-25.56412800000001</v>
+        <v>-36.42159500000001</v>
       </c>
       <c r="O36">
-        <v>-5.112825600000003</v>
+        <v>-7.284319000000003</v>
       </c>
       <c r="P36">
-        <v>-20.45130240000001</v>
+        <v>-29.13727600000001</v>
       </c>
       <c r="Q36">
-        <v>26.74869759999999</v>
+        <v>18.062724</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0875540104628017</v>
+        <v>0.0884216690959731</v>
       </c>
       <c r="T36">
-        <v>0.7920581494179324</v>
+        <v>0.8085173130694931</v>
       </c>
       <c r="U36">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1016558692809773</v>
+        <v>0.08409365694354641</v>
       </c>
       <c r="W36">
-        <v>0.1803875014483798</v>
+        <v>0.2159707156927118</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.5082793464048867</v>
+        <v>0.420468284717732</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1330638354048316</v>
+        <v>0.1349638354048316</v>
       </c>
       <c r="C37">
-        <v>-11.2366014197417</v>
+        <v>-23.84513908101755</v>
       </c>
       <c r="D37">
-        <v>241.0883985802583</v>
+        <v>236.0948609189825</v>
       </c>
       <c r="E37">
-        <v>-95.67499999999995</v>
+        <v>-88.05999999999995</v>
       </c>
       <c r="F37">
-        <v>266.525</v>
+        <v>274.14</v>
       </c>
       <c r="G37">
         <v>14.2</v>
@@ -4321,37 +4321,37 @@
         <v>26.425</v>
       </c>
       <c r="M37">
-        <v>62.84659500000001</v>
+        <v>64.64221200000001</v>
       </c>
       <c r="N37">
-        <v>-36.42159500000001</v>
+        <v>-38.21721200000002</v>
       </c>
       <c r="O37">
-        <v>-7.284319000000003</v>
+        <v>-7.643442400000004</v>
       </c>
       <c r="P37">
-        <v>-29.13727600000001</v>
+        <v>-30.57376960000001</v>
       </c>
       <c r="Q37">
-        <v>18.062724</v>
+        <v>16.62623039999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0884216690959731</v>
+        <v>0.08908763267559769</v>
       </c>
       <c r="T37">
-        <v>0.8085173130694931</v>
+        <v>0.821150396086204</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.08409365694354641</v>
+        <v>0.08175772202844789</v>
       </c>
       <c r="W37">
-        <v>0.2159707156927118</v>
+        <v>0.216521529145692</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.420468284717732</v>
+        <v>0.4087886101422394</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1349638354048316</v>
+        <v>0.1368638354048316</v>
       </c>
       <c r="C38">
-        <v>-23.84513908101749</v>
+        <v>-36.25101726427204</v>
       </c>
       <c r="D38">
-        <v>236.0948609189825</v>
+        <v>231.303982735728</v>
       </c>
       <c r="E38">
-        <v>-88.06</v>
+        <v>-80.44499999999999</v>
       </c>
       <c r="F38">
-        <v>274.14</v>
+        <v>281.755</v>
       </c>
       <c r="G38">
         <v>14.2</v>
@@ -4403,37 +4403,37 @@
         <v>26.425</v>
       </c>
       <c r="M38">
-        <v>64.642212</v>
+        <v>66.43782900000001</v>
       </c>
       <c r="N38">
-        <v>-38.217212</v>
+        <v>-40.01282900000001</v>
       </c>
       <c r="O38">
-        <v>-7.643442400000001</v>
+        <v>-8.002565800000003</v>
       </c>
       <c r="P38">
-        <v>-30.5737696</v>
+        <v>-32.01026320000001</v>
       </c>
       <c r="Q38">
-        <v>16.6262304</v>
+        <v>15.18973679999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08908763267559769</v>
+        <v>0.08977473795616273</v>
       </c>
       <c r="T38">
-        <v>0.8211503960862039</v>
+        <v>0.8341845293574135</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.0817577220284479</v>
+        <v>0.07954805386551687</v>
       </c>
       <c r="W38">
-        <v>0.216521529145692</v>
+        <v>0.2170425688985111</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4087886101422396</v>
+        <v>0.3977402693275843</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1368638354048316</v>
+        <v>0.1387638354048316</v>
       </c>
       <c r="C39">
-        <v>-36.25101726427204</v>
+        <v>-48.46632780452435</v>
       </c>
       <c r="D39">
-        <v>231.303982735728</v>
+        <v>226.7036721954757</v>
       </c>
       <c r="E39">
-        <v>-80.44499999999999</v>
+        <v>-72.82999999999998</v>
       </c>
       <c r="F39">
-        <v>281.755</v>
+        <v>289.37</v>
       </c>
       <c r="G39">
         <v>14.2</v>
@@ -4485,37 +4485,37 @@
         <v>26.425</v>
       </c>
       <c r="M39">
-        <v>66.43782900000001</v>
+        <v>68.233446</v>
       </c>
       <c r="N39">
-        <v>-40.01282900000001</v>
+        <v>-41.808446</v>
       </c>
       <c r="O39">
-        <v>-8.002565800000003</v>
+        <v>-8.361689200000001</v>
       </c>
       <c r="P39">
-        <v>-32.01026320000001</v>
+        <v>-33.4467568</v>
       </c>
       <c r="Q39">
-        <v>15.18973679999999</v>
+        <v>13.7532432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08977473795616273</v>
+        <v>0.09048400792319761</v>
       </c>
       <c r="T39">
-        <v>0.8341845293574135</v>
+        <v>0.8476391185405976</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07954805386551687</v>
+        <v>0.07745468402695066</v>
       </c>
       <c r="W39">
-        <v>0.2170425688985111</v>
+        <v>0.217536185506445</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3977402693275843</v>
+        <v>0.3872734201347532</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1387638354048316</v>
+        <v>0.1406638354048316</v>
       </c>
       <c r="C40">
-        <v>-48.46632780452435</v>
+        <v>-60.50221933740835</v>
       </c>
       <c r="D40">
-        <v>226.7036721954757</v>
+        <v>222.2827806625917</v>
       </c>
       <c r="E40">
-        <v>-72.82999999999998</v>
+        <v>-65.21499999999997</v>
       </c>
       <c r="F40">
-        <v>289.37</v>
+        <v>296.985</v>
       </c>
       <c r="G40">
         <v>14.2</v>
@@ -4567,37 +4567,37 @@
         <v>26.425</v>
       </c>
       <c r="M40">
-        <v>68.233446</v>
+        <v>70.02906300000001</v>
       </c>
       <c r="N40">
-        <v>-41.808446</v>
+        <v>-43.60406300000001</v>
       </c>
       <c r="O40">
-        <v>-8.361689200000001</v>
+        <v>-8.720812600000002</v>
       </c>
       <c r="P40">
-        <v>-33.4467568</v>
+        <v>-34.88325040000001</v>
       </c>
       <c r="Q40">
-        <v>13.7532432</v>
+        <v>12.31674959999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09048400792319761</v>
+        <v>0.09121653264325003</v>
       </c>
       <c r="T40">
-        <v>0.8476391185405976</v>
+        <v>0.8615348417953613</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07745468402695066</v>
+        <v>0.07546866648779806</v>
       </c>
       <c r="W40">
-        <v>0.217536185506445</v>
+        <v>0.2180044884421772</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3872734201347532</v>
+        <v>0.3773433324389903</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1406638354048316</v>
+        <v>0.1425638354048316</v>
       </c>
       <c r="C41">
-        <v>-60.50221933740835</v>
+        <v>-72.36898750555557</v>
       </c>
       <c r="D41">
-        <v>222.2827806625917</v>
+        <v>218.0310124944445</v>
       </c>
       <c r="E41">
-        <v>-65.21499999999997</v>
+        <v>-57.59999999999997</v>
       </c>
       <c r="F41">
-        <v>296.985</v>
+        <v>304.6</v>
       </c>
       <c r="G41">
         <v>14.2</v>
@@ -4649,37 +4649,37 @@
         <v>26.425</v>
       </c>
       <c r="M41">
-        <v>70.02906300000001</v>
+        <v>71.82468000000001</v>
       </c>
       <c r="N41">
-        <v>-43.60406300000001</v>
+        <v>-45.39968000000002</v>
       </c>
       <c r="O41">
-        <v>-8.720812600000002</v>
+        <v>-9.079936000000004</v>
       </c>
       <c r="P41">
-        <v>-34.88325040000001</v>
+        <v>-36.31974400000001</v>
       </c>
       <c r="Q41">
-        <v>12.31674959999999</v>
+        <v>10.88025599999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09121653264325003</v>
+        <v>0.09197347485397087</v>
       </c>
       <c r="T41">
-        <v>0.8615348417953613</v>
+        <v>0.8758937558252842</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07546866648779806</v>
+        <v>0.07358194982560311</v>
       </c>
       <c r="W41">
-        <v>0.2180044884421772</v>
+        <v>0.2184493762311228</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3773433324389903</v>
+        <v>0.3679097491280154</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1425638354048316</v>
+        <v>0.1444638354048316</v>
       </c>
       <c r="C42">
-        <v>-72.36898750555557</v>
+        <v>-84.07615500661709</v>
       </c>
       <c r="D42">
-        <v>218.0310124944445</v>
+        <v>213.938844993383</v>
       </c>
       <c r="E42">
-        <v>-57.59999999999997</v>
+        <v>-49.98499999999996</v>
       </c>
       <c r="F42">
-        <v>304.6</v>
+        <v>312.215</v>
       </c>
       <c r="G42">
         <v>14.2</v>
@@ -4731,37 +4731,37 @@
         <v>26.425</v>
       </c>
       <c r="M42">
-        <v>71.82468000000001</v>
+        <v>73.62029700000001</v>
       </c>
       <c r="N42">
-        <v>-45.39968000000002</v>
+        <v>-47.19529700000001</v>
       </c>
       <c r="O42">
-        <v>-9.079936000000004</v>
+        <v>-9.439059400000003</v>
       </c>
       <c r="P42">
-        <v>-36.31974400000001</v>
+        <v>-37.75623760000001</v>
       </c>
       <c r="Q42">
-        <v>10.88025599999999</v>
+        <v>9.443762399999997</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09197347485397087</v>
+        <v>0.09275607612268223</v>
       </c>
       <c r="T42">
-        <v>0.8758937558252842</v>
+        <v>0.8907394127036788</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07358194982560311</v>
+        <v>0.07178726812253962</v>
       </c>
       <c r="W42">
-        <v>0.2184493762311228</v>
+        <v>0.2188725621767051</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3679097491280154</v>
+        <v>0.3589363406126981</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1444638354048316</v>
+        <v>0.1463638354048316</v>
       </c>
       <c r="C43">
-        <v>-84.07615500661709</v>
+        <v>-95.63254279295381</v>
       </c>
       <c r="D43">
-        <v>213.938844993383</v>
+        <v>209.9974572070462</v>
       </c>
       <c r="E43">
-        <v>-49.98499999999996</v>
+        <v>-42.36999999999995</v>
       </c>
       <c r="F43">
-        <v>312.215</v>
+        <v>319.83</v>
       </c>
       <c r="G43">
         <v>14.2</v>
@@ -4813,37 +4813,37 @@
         <v>26.425</v>
       </c>
       <c r="M43">
-        <v>73.62029700000001</v>
+        <v>75.41591400000001</v>
       </c>
       <c r="N43">
-        <v>-47.19529700000001</v>
+        <v>-48.99091400000002</v>
       </c>
       <c r="O43">
-        <v>-9.439059400000003</v>
+        <v>-9.798182800000005</v>
       </c>
       <c r="P43">
-        <v>-37.75623760000001</v>
+        <v>-39.19273120000001</v>
       </c>
       <c r="Q43">
-        <v>9.443762399999997</v>
+        <v>8.007268799999991</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09275607612268223</v>
+        <v>0.09356566364203882</v>
       </c>
       <c r="T43">
-        <v>0.8907394127036788</v>
+        <v>0.9060969887847767</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07178726812253962</v>
+        <v>0.07007804745295533</v>
       </c>
       <c r="W43">
-        <v>0.2188725621767051</v>
+        <v>0.2192755964105931</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3589363406126981</v>
+        <v>0.3503902372647767</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1463638354048316</v>
+        <v>0.1482638354048317</v>
       </c>
       <c r="C44">
-        <v>-95.63254279295376</v>
+        <v>-107.0463335434411</v>
       </c>
       <c r="D44">
-        <v>209.9974572070462</v>
+        <v>206.1986664565589</v>
       </c>
       <c r="E44">
-        <v>-42.37</v>
+        <v>-34.755</v>
       </c>
       <c r="F44">
-        <v>319.83</v>
+        <v>327.445</v>
       </c>
       <c r="G44">
         <v>14.2</v>
@@ -4895,37 +4895,37 @@
         <v>26.425</v>
       </c>
       <c r="M44">
-        <v>75.415914</v>
+        <v>77.21153100000001</v>
       </c>
       <c r="N44">
-        <v>-48.990914</v>
+        <v>-50.78653100000001</v>
       </c>
       <c r="O44">
-        <v>-9.798182800000001</v>
+        <v>-10.1573062</v>
       </c>
       <c r="P44">
-        <v>-39.1927312</v>
+        <v>-40.62922480000001</v>
       </c>
       <c r="Q44">
-        <v>8.007268799999999</v>
+        <v>6.570775199999993</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09356566364203882</v>
+        <v>0.09440365774102195</v>
       </c>
       <c r="T44">
-        <v>0.9060969887847766</v>
+        <v>0.9219934271845096</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07007804745295536</v>
+        <v>0.06844832541916568</v>
       </c>
       <c r="W44">
-        <v>0.2192755964105931</v>
+        <v>0.2196598848661608</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3503902372647767</v>
+        <v>0.3422416270958284</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1482638354048317</v>
+        <v>0.1501638354048316</v>
       </c>
       <c r="C45">
-        <v>-107.0463335434411</v>
+        <v>-118.3251283685663</v>
       </c>
       <c r="D45">
-        <v>206.1986664565589</v>
+        <v>202.5348716314337</v>
       </c>
       <c r="E45">
-        <v>-34.755</v>
+        <v>-27.13999999999999</v>
       </c>
       <c r="F45">
-        <v>327.445</v>
+        <v>335.06</v>
       </c>
       <c r="G45">
         <v>14.2</v>
@@ -4977,37 +4977,37 @@
         <v>26.425</v>
       </c>
       <c r="M45">
-        <v>77.21153100000001</v>
+        <v>79.007148</v>
       </c>
       <c r="N45">
-        <v>-50.78653100000001</v>
+        <v>-52.582148</v>
       </c>
       <c r="O45">
-        <v>-10.1573062</v>
+        <v>-10.5164296</v>
       </c>
       <c r="P45">
-        <v>-40.62922480000001</v>
+        <v>-42.0657184</v>
       </c>
       <c r="Q45">
-        <v>6.570775199999993</v>
+        <v>5.134281600000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09440365774102195</v>
+        <v>0.09527158020068306</v>
       </c>
       <c r="T45">
-        <v>0.9219934271845096</v>
+        <v>0.9384575955270901</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06844832541916568</v>
+        <v>0.0668926816596392</v>
       </c>
       <c r="W45">
-        <v>0.2196598848661608</v>
+        <v>0.2200267056646571</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3422416270958284</v>
+        <v>0.334463408298196</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1501638354048316</v>
+        <v>0.1520638354048316</v>
       </c>
       <c r="C46">
-        <v>-118.3251283685663</v>
+        <v>-129.4759975757546</v>
       </c>
       <c r="D46">
-        <v>202.5348716314337</v>
+        <v>198.9990024242454</v>
       </c>
       <c r="E46">
-        <v>-27.13999999999999</v>
+        <v>-19.52499999999998</v>
       </c>
       <c r="F46">
-        <v>335.06</v>
+        <v>342.675</v>
       </c>
       <c r="G46">
         <v>14.2</v>
@@ -5059,37 +5059,37 @@
         <v>26.425</v>
       </c>
       <c r="M46">
-        <v>79.007148</v>
+        <v>80.80276500000001</v>
       </c>
       <c r="N46">
-        <v>-52.582148</v>
+        <v>-54.37776500000001</v>
       </c>
       <c r="O46">
-        <v>-10.5164296</v>
+        <v>-10.875553</v>
       </c>
       <c r="P46">
-        <v>-42.0657184</v>
+        <v>-43.50221200000001</v>
       </c>
       <c r="Q46">
-        <v>5.134281600000001</v>
+        <v>3.697787999999996</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09527158020068306</v>
+        <v>0.09617106347705912</v>
       </c>
       <c r="T46">
-        <v>0.9384575955270901</v>
+        <v>0.95552046090031</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0668926816596392</v>
+        <v>0.06540617762275833</v>
       </c>
       <c r="W46">
-        <v>0.2200267056646571</v>
+        <v>0.2203772233165536</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.334463408298196</v>
+        <v>0.3270308881137916</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1520638354048316</v>
+        <v>0.1539638354048316</v>
       </c>
       <c r="C47">
-        <v>-129.4759975757546</v>
+        <v>-140.5055262083473</v>
       </c>
       <c r="D47">
-        <v>198.9990024242454</v>
+        <v>195.5844737916527</v>
       </c>
       <c r="E47">
-        <v>-19.52499999999998</v>
+        <v>-11.90999999999997</v>
       </c>
       <c r="F47">
-        <v>342.675</v>
+        <v>350.29</v>
       </c>
       <c r="G47">
         <v>14.2</v>
@@ -5141,37 +5141,37 @@
         <v>26.425</v>
       </c>
       <c r="M47">
-        <v>80.80276500000001</v>
+        <v>82.59838200000002</v>
       </c>
       <c r="N47">
-        <v>-54.37776500000001</v>
+        <v>-56.17338200000002</v>
       </c>
       <c r="O47">
-        <v>-10.875553</v>
+        <v>-11.23467640000001</v>
       </c>
       <c r="P47">
-        <v>-43.50221200000001</v>
+        <v>-44.93870560000001</v>
       </c>
       <c r="Q47">
-        <v>3.697787999999996</v>
+        <v>2.26129439999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09617106347705912</v>
+        <v>0.09710386094885651</v>
       </c>
       <c r="T47">
-        <v>0.95552046090031</v>
+        <v>0.9732152842503158</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06540617762275833</v>
+        <v>0.06398430419617661</v>
       </c>
       <c r="W47">
-        <v>0.2203772233165536</v>
+        <v>0.2207125010705416</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3270308881137916</v>
+        <v>0.319921520980883</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1539638354048316</v>
+        <v>0.1558638354048316</v>
       </c>
       <c r="C48">
-        <v>-140.5055262083473</v>
+        <v>-151.4198549753785</v>
       </c>
       <c r="D48">
-        <v>195.5844737916527</v>
+        <v>192.2851450246216</v>
       </c>
       <c r="E48">
-        <v>-11.90999999999997</v>
+        <v>-4.294999999999959</v>
       </c>
       <c r="F48">
-        <v>350.29</v>
+        <v>357.905</v>
       </c>
       <c r="G48">
         <v>14.2</v>
@@ -5223,37 +5223,37 @@
         <v>26.425</v>
       </c>
       <c r="M48">
-        <v>82.59838200000002</v>
+        <v>84.39399900000001</v>
       </c>
       <c r="N48">
-        <v>-56.17338200000002</v>
+        <v>-57.96899900000001</v>
       </c>
       <c r="O48">
-        <v>-11.23467640000001</v>
+        <v>-11.5937998</v>
       </c>
       <c r="P48">
-        <v>-44.93870560000001</v>
+        <v>-46.37519920000001</v>
       </c>
       <c r="Q48">
-        <v>2.26129439999999</v>
+        <v>0.8248007999999913</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09710386094885651</v>
+        <v>0.09807185832525003</v>
       </c>
       <c r="T48">
-        <v>0.9732152842503158</v>
+        <v>0.9915778367833405</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06398430419617661</v>
+        <v>0.06262293602178988</v>
       </c>
       <c r="W48">
-        <v>0.2207125010705416</v>
+        <v>0.2210335116860619</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.319921520980883</v>
+        <v>0.3131146801089494</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1558638354048316</v>
+        <v>0.1577638354048317</v>
       </c>
       <c r="C49">
-        <v>-151.4198549753785</v>
+        <v>-162.2247171073905</v>
       </c>
       <c r="D49">
-        <v>192.2851450246216</v>
+        <v>189.0952828926096</v>
       </c>
       <c r="E49">
-        <v>-4.294999999999959</v>
+        <v>3.32000000000005</v>
       </c>
       <c r="F49">
-        <v>357.905</v>
+        <v>365.52</v>
       </c>
       <c r="G49">
         <v>14.2</v>
@@ -5305,37 +5305,37 @@
         <v>26.425</v>
       </c>
       <c r="M49">
-        <v>84.39399900000001</v>
+        <v>86.18961600000002</v>
       </c>
       <c r="N49">
-        <v>-57.96899900000001</v>
+        <v>-59.76461600000002</v>
       </c>
       <c r="O49">
-        <v>-11.5937998</v>
+        <v>-11.9529232</v>
       </c>
       <c r="P49">
-        <v>-46.37519920000001</v>
+        <v>-47.81169280000002</v>
       </c>
       <c r="Q49">
-        <v>0.8248007999999913</v>
+        <v>-0.6116928000000144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09807185832525003</v>
+        <v>0.09907708636996637</v>
       </c>
       <c r="T49">
-        <v>0.9915778367833405</v>
+        <v>1.010646641336866</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06262293602178988</v>
+        <v>0.06131829152133592</v>
       </c>
       <c r="W49">
-        <v>0.2210335116860619</v>
+        <v>0.221341146859269</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3131146801089494</v>
+        <v>0.3065914576066796</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1577638354048316</v>
+        <v>0.1596638354048316</v>
       </c>
       <c r="C50">
-        <v>-162.2247171073904</v>
+        <v>-172.9254716036565</v>
       </c>
       <c r="D50">
-        <v>189.0952828926096</v>
+        <v>186.0095283963435</v>
       </c>
       <c r="E50">
-        <v>3.319999999999993</v>
+        <v>10.935</v>
       </c>
       <c r="F50">
-        <v>365.52</v>
+        <v>373.135</v>
       </c>
       <c r="G50">
         <v>14.2</v>
@@ -5387,37 +5387,37 @@
         <v>26.425</v>
       </c>
       <c r="M50">
-        <v>86.189616</v>
+        <v>87.98523300000001</v>
       </c>
       <c r="N50">
-        <v>-59.764616</v>
+        <v>-61.56023300000001</v>
       </c>
       <c r="O50">
-        <v>-11.9529232</v>
+        <v>-12.3120466</v>
       </c>
       <c r="P50">
-        <v>-47.8116928</v>
+        <v>-49.24818640000001</v>
       </c>
       <c r="Q50">
-        <v>-0.6116928000000001</v>
+        <v>-2.048186400000006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09907708636996637</v>
+        <v>0.1001217351223187</v>
       </c>
       <c r="T50">
-        <v>1.010646641336866</v>
+        <v>1.030463242147393</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06131829152133594</v>
+        <v>0.06006689781681887</v>
       </c>
       <c r="W50">
-        <v>0.221341146859269</v>
+        <v>0.2216362254947941</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3065914576066796</v>
+        <v>0.3003344890840943</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1596638354048316</v>
+        <v>0.1615638354048316</v>
       </c>
       <c r="C51">
-        <v>-172.9254716036565</v>
+        <v>-183.5271332763995</v>
       </c>
       <c r="D51">
-        <v>186.0095283963435</v>
+        <v>183.0228667236005</v>
       </c>
       <c r="E51">
-        <v>10.935</v>
+        <v>18.55000000000001</v>
       </c>
       <c r="F51">
-        <v>373.135</v>
+        <v>380.75</v>
       </c>
       <c r="G51">
         <v>14.2</v>
@@ -5469,37 +5469,37 @@
         <v>26.425</v>
       </c>
       <c r="M51">
-        <v>87.98523300000001</v>
+        <v>89.78085</v>
       </c>
       <c r="N51">
-        <v>-61.56023300000001</v>
+        <v>-63.35585</v>
       </c>
       <c r="O51">
-        <v>-12.3120466</v>
+        <v>-12.67117</v>
       </c>
       <c r="P51">
-        <v>-49.24818640000001</v>
+        <v>-50.68468</v>
       </c>
       <c r="Q51">
-        <v>-2.048186400000006</v>
+        <v>-3.484679999999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1001217351223187</v>
+        <v>0.101208169824765</v>
       </c>
       <c r="T51">
-        <v>1.030463242147393</v>
+        <v>1.051072506990341</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06006689781681887</v>
+        <v>0.05886555986048249</v>
       </c>
       <c r="W51">
-        <v>0.2216362254947941</v>
+        <v>0.2219195009848982</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3003344890840943</v>
+        <v>0.2943277993024125</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1615638354048316</v>
+        <v>0.1634638354048316</v>
       </c>
       <c r="C52">
-        <v>-183.5271332763995</v>
+        <v>-194.0343999463208</v>
       </c>
       <c r="D52">
-        <v>183.0228667236005</v>
+        <v>180.1306000536792</v>
       </c>
       <c r="E52">
-        <v>18.55000000000001</v>
+        <v>26.16500000000002</v>
       </c>
       <c r="F52">
-        <v>380.75</v>
+        <v>388.365</v>
       </c>
       <c r="G52">
         <v>14.2</v>
@@ -5551,37 +5551,37 @@
         <v>26.425</v>
       </c>
       <c r="M52">
-        <v>89.78085</v>
+        <v>91.57646700000001</v>
       </c>
       <c r="N52">
-        <v>-63.35585</v>
+        <v>-65.15146700000001</v>
       </c>
       <c r="O52">
-        <v>-12.67117</v>
+        <v>-13.0302934</v>
       </c>
       <c r="P52">
-        <v>-50.68468</v>
+        <v>-52.12117360000001</v>
       </c>
       <c r="Q52">
-        <v>-3.484679999999997</v>
+        <v>-4.921173600000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.101208169824765</v>
+        <v>0.1023389488007806</v>
       </c>
       <c r="T52">
-        <v>1.051072506990341</v>
+        <v>1.072522966316674</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05886555986048249</v>
+        <v>0.05771133319655147</v>
       </c>
       <c r="W52">
-        <v>0.2219195009848982</v>
+        <v>0.2221916676322532</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2943277993024125</v>
+        <v>0.2885566659827573</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1634638354048316</v>
+        <v>0.1653638354048316</v>
       </c>
       <c r="C53">
-        <v>-194.0343999463208</v>
+        <v>-204.4516770996574</v>
       </c>
       <c r="D53">
-        <v>180.1306000536792</v>
+        <v>177.3283229003426</v>
       </c>
       <c r="E53">
-        <v>26.16500000000002</v>
+        <v>33.78000000000003</v>
       </c>
       <c r="F53">
-        <v>388.365</v>
+        <v>395.98</v>
       </c>
       <c r="G53">
         <v>14.2</v>
@@ -5633,37 +5633,37 @@
         <v>26.425</v>
       </c>
       <c r="M53">
-        <v>91.57646700000001</v>
+        <v>93.37208400000002</v>
       </c>
       <c r="N53">
-        <v>-65.15146700000001</v>
+        <v>-66.94708400000002</v>
       </c>
       <c r="O53">
-        <v>-13.0302934</v>
+        <v>-13.3894168</v>
       </c>
       <c r="P53">
-        <v>-52.12117360000001</v>
+        <v>-53.55766720000001</v>
       </c>
       <c r="Q53">
-        <v>-4.921173600000003</v>
+        <v>-6.357667200000009</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1023389488007806</v>
+        <v>0.1035168435674636</v>
       </c>
       <c r="T53">
-        <v>1.072522966316674</v>
+        <v>1.094867194781605</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05771133319655147</v>
+        <v>0.05660149986584854</v>
       </c>
       <c r="W53">
-        <v>0.2221916676322532</v>
+        <v>0.2224533663316329</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2885566659827573</v>
+        <v>0.2830074993292427</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1653638354048316</v>
+        <v>0.1672638354048316</v>
       </c>
       <c r="C54">
-        <v>-204.4516770996574</v>
+        <v>-214.783100278968</v>
       </c>
       <c r="D54">
-        <v>177.3283229003426</v>
+        <v>174.6118997210321</v>
       </c>
       <c r="E54">
-        <v>33.78000000000003</v>
+        <v>41.39500000000004</v>
       </c>
       <c r="F54">
-        <v>395.98</v>
+        <v>403.595</v>
       </c>
       <c r="G54">
         <v>14.2</v>
@@ -5715,37 +5715,37 @@
         <v>26.425</v>
       </c>
       <c r="M54">
-        <v>93.37208400000002</v>
+        <v>95.16770100000001</v>
       </c>
       <c r="N54">
-        <v>-66.94708400000002</v>
+        <v>-68.74270100000001</v>
       </c>
       <c r="O54">
-        <v>-13.3894168</v>
+        <v>-13.7485402</v>
       </c>
       <c r="P54">
-        <v>-53.55766720000001</v>
+        <v>-54.99416080000001</v>
       </c>
       <c r="Q54">
-        <v>-6.357667200000009</v>
+        <v>-7.794160800000007</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1035168435674636</v>
+        <v>0.1047448615157075</v>
       </c>
       <c r="T54">
-        <v>1.094867194781605</v>
+        <v>1.118162241479086</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05660149986584854</v>
+        <v>0.05553354703819102</v>
       </c>
       <c r="W54">
-        <v>0.2224533663316329</v>
+        <v>0.2227051896083946</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2830074993292427</v>
+        <v>0.2776677351909551</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1672638354048316</v>
+        <v>0.1691638354048317</v>
       </c>
       <c r="C55">
-        <v>-214.783100278968</v>
+        <v>-225.032555446995</v>
       </c>
       <c r="D55">
-        <v>174.6118997210321</v>
+        <v>171.977444553005</v>
       </c>
       <c r="E55">
-        <v>41.39500000000004</v>
+        <v>49.01000000000005</v>
       </c>
       <c r="F55">
-        <v>403.595</v>
+        <v>411.21</v>
       </c>
       <c r="G55">
         <v>14.2</v>
@@ -5797,37 +5797,37 @@
         <v>26.425</v>
       </c>
       <c r="M55">
-        <v>95.16770100000001</v>
+        <v>96.96331800000002</v>
       </c>
       <c r="N55">
-        <v>-68.74270100000001</v>
+        <v>-70.53831800000002</v>
       </c>
       <c r="O55">
-        <v>-13.7485402</v>
+        <v>-14.1076636</v>
       </c>
       <c r="P55">
-        <v>-54.99416080000001</v>
+        <v>-56.43065440000002</v>
       </c>
       <c r="Q55">
-        <v>-7.794160800000007</v>
+        <v>-9.230654400000013</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1047448615157075</v>
+        <v>0.1060262715486576</v>
       </c>
       <c r="T55">
-        <v>1.118162241479086</v>
+        <v>1.142470116293849</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05553354703819102</v>
+        <v>0.05450514801896527</v>
       </c>
       <c r="W55">
-        <v>0.2227051896083946</v>
+        <v>0.222947686097128</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2776677351909551</v>
+        <v>0.2725257400948263</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1691638354048317</v>
+        <v>0.1710638354048316</v>
       </c>
       <c r="C56">
-        <v>-225.032555446995</v>
+        <v>-235.2036975344888</v>
       </c>
       <c r="D56">
-        <v>171.977444553005</v>
+        <v>169.4213024655112</v>
       </c>
       <c r="E56">
-        <v>49.01000000000005</v>
+        <v>56.62500000000006</v>
       </c>
       <c r="F56">
-        <v>411.21</v>
+        <v>418.825</v>
       </c>
       <c r="G56">
         <v>14.2</v>
@@ -5879,37 +5879,37 @@
         <v>26.425</v>
       </c>
       <c r="M56">
-        <v>96.96331800000002</v>
+        <v>98.75893500000001</v>
       </c>
       <c r="N56">
-        <v>-70.53831800000002</v>
+        <v>-72.33393500000001</v>
       </c>
       <c r="O56">
-        <v>-14.1076636</v>
+        <v>-14.466787</v>
       </c>
       <c r="P56">
-        <v>-56.43065440000002</v>
+        <v>-57.86714800000001</v>
       </c>
       <c r="Q56">
-        <v>-9.230654400000013</v>
+        <v>-10.667148</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1060262715486576</v>
+        <v>0.1073646331386278</v>
       </c>
       <c r="T56">
-        <v>1.142470116293849</v>
+        <v>1.167858341100379</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05450514801896527</v>
+        <v>0.05351414532771135</v>
       </c>
       <c r="W56">
-        <v>0.222947686097128</v>
+        <v>0.2231813645317257</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2725257400948263</v>
+        <v>0.2675707266385567</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1710638354048316</v>
+        <v>0.1729638354048317</v>
       </c>
       <c r="C57">
-        <v>-235.2036975344888</v>
+        <v>-245.2999673581709</v>
       </c>
       <c r="D57">
-        <v>169.4213024655112</v>
+        <v>166.9400326418292</v>
       </c>
       <c r="E57">
-        <v>56.62500000000006</v>
+        <v>64.24000000000007</v>
       </c>
       <c r="F57">
-        <v>418.825</v>
+        <v>426.4400000000001</v>
       </c>
       <c r="G57">
         <v>14.2</v>
@@ -5961,37 +5961,37 @@
         <v>26.425</v>
       </c>
       <c r="M57">
-        <v>98.75893500000001</v>
+        <v>100.554552</v>
       </c>
       <c r="N57">
-        <v>-72.33393500000001</v>
+        <v>-74.12955200000002</v>
       </c>
       <c r="O57">
-        <v>-14.466787</v>
+        <v>-14.82591040000001</v>
       </c>
       <c r="P57">
-        <v>-57.86714800000001</v>
+        <v>-59.30364160000001</v>
       </c>
       <c r="Q57">
-        <v>-10.667148</v>
+        <v>-12.10364160000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1073646331386278</v>
+        <v>0.1087638293463239</v>
       </c>
       <c r="T57">
-        <v>1.167858341100379</v>
+        <v>1.194400576125388</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05351414532771135</v>
+        <v>0.05255853558971651</v>
       </c>
       <c r="W57">
-        <v>0.2231813645317257</v>
+        <v>0.2234066973079449</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2675707266385567</v>
+        <v>0.2627926779485825</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1729638354048317</v>
+        <v>0.1748638354048316</v>
       </c>
       <c r="C58">
-        <v>-245.2999673581709</v>
+        <v>-255.3246070735198</v>
       </c>
       <c r="D58">
-        <v>166.9400326418292</v>
+        <v>164.5303929264803</v>
       </c>
       <c r="E58">
-        <v>64.24000000000007</v>
+        <v>71.85500000000008</v>
       </c>
       <c r="F58">
-        <v>426.4400000000001</v>
+        <v>434.0550000000001</v>
       </c>
       <c r="G58">
         <v>14.2</v>
@@ -6043,37 +6043,37 @@
         <v>26.425</v>
       </c>
       <c r="M58">
-        <v>100.554552</v>
+        <v>102.350169</v>
       </c>
       <c r="N58">
-        <v>-74.12955200000002</v>
+        <v>-75.92516900000003</v>
       </c>
       <c r="O58">
-        <v>-14.82591040000001</v>
+        <v>-15.18503380000001</v>
       </c>
       <c r="P58">
-        <v>-59.30364160000001</v>
+        <v>-60.74013520000002</v>
       </c>
       <c r="Q58">
-        <v>-12.10364160000001</v>
+        <v>-13.54013520000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1087638293463239</v>
+        <v>0.1102281044474012</v>
       </c>
       <c r="T58">
-        <v>1.194400576125388</v>
+        <v>1.222177333709699</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05255853558971651</v>
+        <v>0.05163645601796708</v>
       </c>
       <c r="W58">
-        <v>0.2234066973079449</v>
+        <v>0.2236241236709634</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2627926779485825</v>
+        <v>0.2581822800898355</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1748638354048316</v>
+        <v>0.1767638354048316</v>
       </c>
       <c r="C59">
-        <v>-255.3246070735198</v>
+        <v>-265.2806743083086</v>
       </c>
       <c r="D59">
-        <v>164.5303929264803</v>
+        <v>162.1893256916915</v>
       </c>
       <c r="E59">
-        <v>71.85500000000008</v>
+        <v>79.47000000000008</v>
       </c>
       <c r="F59">
-        <v>434.0550000000001</v>
+        <v>441.6700000000001</v>
       </c>
       <c r="G59">
         <v>14.2</v>
@@ -6125,37 +6125,37 @@
         <v>26.425</v>
       </c>
       <c r="M59">
-        <v>102.350169</v>
+        <v>104.145786</v>
       </c>
       <c r="N59">
-        <v>-75.92516900000003</v>
+        <v>-77.72078600000002</v>
       </c>
       <c r="O59">
-        <v>-15.18503380000001</v>
+        <v>-15.5441572</v>
       </c>
       <c r="P59">
-        <v>-60.74013520000002</v>
+        <v>-62.17662880000002</v>
       </c>
       <c r="Q59">
-        <v>-13.54013520000002</v>
+        <v>-14.97662880000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1102281044474012</v>
+        <v>0.1117621069342441</v>
       </c>
       <c r="T59">
-        <v>1.222177333709699</v>
+        <v>1.25127679403612</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05163645601796708</v>
+        <v>0.05074617229351938</v>
       </c>
       <c r="W59">
-        <v>0.2236241236709634</v>
+        <v>0.2238340525731881</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2581822800898355</v>
+        <v>0.2537308614675969</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1767638354048316</v>
+        <v>0.1786638354048316</v>
       </c>
       <c r="C60">
-        <v>-265.2806743083085</v>
+        <v>-275.1710551064532</v>
       </c>
       <c r="D60">
-        <v>162.1893256916915</v>
+        <v>159.9139448935468</v>
       </c>
       <c r="E60">
-        <v>79.46999999999997</v>
+        <v>87.08499999999998</v>
       </c>
       <c r="F60">
-        <v>441.67</v>
+        <v>449.285</v>
       </c>
       <c r="G60">
         <v>14.2</v>
@@ -6207,37 +6207,37 @@
         <v>26.425</v>
       </c>
       <c r="M60">
-        <v>104.145786</v>
+        <v>105.941403</v>
       </c>
       <c r="N60">
-        <v>-77.720786</v>
+        <v>-79.516403</v>
       </c>
       <c r="O60">
-        <v>-15.5441572</v>
+        <v>-15.9032806</v>
       </c>
       <c r="P60">
-        <v>-62.1766288</v>
+        <v>-63.61312239999999</v>
       </c>
       <c r="Q60">
-        <v>-14.9766288</v>
+        <v>-16.41312239999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1117621069342441</v>
+        <v>0.113370938810689</v>
       </c>
       <c r="T60">
-        <v>1.25127679403612</v>
+        <v>1.281795740232123</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05074617229351939</v>
+        <v>0.049886067678375</v>
       </c>
       <c r="W60">
-        <v>0.2238340525731881</v>
+        <v>0.2240368652414392</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2537308614675969</v>
+        <v>0.249430338391875</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1786638354048316</v>
+        <v>0.1805638354048316</v>
       </c>
       <c r="C61">
-        <v>-275.1710551064532</v>
+        <v>-284.9984757973864</v>
       </c>
       <c r="D61">
-        <v>159.9139448935468</v>
+        <v>157.7015242026136</v>
       </c>
       <c r="E61">
-        <v>87.08499999999998</v>
+        <v>94.69999999999999</v>
       </c>
       <c r="F61">
-        <v>449.285</v>
+        <v>456.9</v>
       </c>
       <c r="G61">
         <v>14.2</v>
@@ -6289,37 +6289,37 @@
         <v>26.425</v>
       </c>
       <c r="M61">
-        <v>105.941403</v>
+        <v>107.73702</v>
       </c>
       <c r="N61">
-        <v>-79.516403</v>
+        <v>-81.31202</v>
       </c>
       <c r="O61">
-        <v>-15.9032806</v>
+        <v>-16.262404</v>
       </c>
       <c r="P61">
-        <v>-63.61312239999999</v>
+        <v>-65.049616</v>
       </c>
       <c r="Q61">
-        <v>-16.41312239999999</v>
+        <v>-17.849616</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.113370938810689</v>
+        <v>0.1150602122809563</v>
       </c>
       <c r="T61">
-        <v>1.281795740232123</v>
+        <v>1.313840633737926</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.049886067678375</v>
+        <v>0.04905463321706875</v>
       </c>
       <c r="W61">
-        <v>0.2240368652414392</v>
+        <v>0.2242329174874152</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.249430338391875</v>
+        <v>0.2452731660853437</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1805638354048316</v>
+        <v>0.1824638354048316</v>
       </c>
       <c r="C62">
-        <v>-284.9984757973864</v>
+        <v>-294.7655138935941</v>
       </c>
       <c r="D62">
-        <v>157.7015242026136</v>
+        <v>155.5494861064059</v>
       </c>
       <c r="E62">
-        <v>94.69999999999999</v>
+        <v>102.315</v>
       </c>
       <c r="F62">
-        <v>456.9</v>
+        <v>464.515</v>
       </c>
       <c r="G62">
         <v>14.2</v>
@@ -6371,37 +6371,37 @@
         <v>26.425</v>
       </c>
       <c r="M62">
-        <v>107.73702</v>
+        <v>109.532637</v>
       </c>
       <c r="N62">
-        <v>-81.31202</v>
+        <v>-83.10763700000001</v>
       </c>
       <c r="O62">
-        <v>-16.262404</v>
+        <v>-16.6215274</v>
       </c>
       <c r="P62">
-        <v>-65.049616</v>
+        <v>-66.48610960000001</v>
       </c>
       <c r="Q62">
-        <v>-17.849616</v>
+        <v>-19.2861096</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1150602122809563</v>
+        <v>0.1168361151599552</v>
       </c>
       <c r="T62">
-        <v>1.313840633737926</v>
+        <v>1.347528855115822</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04905463321706875</v>
+        <v>0.04825045890203483</v>
       </c>
       <c r="W62">
-        <v>0.2242329174874152</v>
+        <v>0.2244225417909002</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2452731660853437</v>
+        <v>0.2412522945101742</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1824638354048316</v>
+        <v>0.1843638354048316</v>
       </c>
       <c r="C63">
-        <v>-294.7655138935941</v>
+        <v>-304.4746081079026</v>
       </c>
       <c r="D63">
-        <v>155.5494861064059</v>
+        <v>153.4553918920974</v>
       </c>
       <c r="E63">
-        <v>102.315</v>
+        <v>109.93</v>
       </c>
       <c r="F63">
-        <v>464.515</v>
+        <v>472.13</v>
       </c>
       <c r="G63">
         <v>14.2</v>
@@ -6453,37 +6453,37 @@
         <v>26.425</v>
       </c>
       <c r="M63">
-        <v>109.532637</v>
+        <v>111.328254</v>
       </c>
       <c r="N63">
-        <v>-83.10763700000001</v>
+        <v>-84.903254</v>
       </c>
       <c r="O63">
-        <v>-16.6215274</v>
+        <v>-16.9806508</v>
       </c>
       <c r="P63">
-        <v>-66.48610960000001</v>
+        <v>-67.9226032</v>
       </c>
       <c r="Q63">
-        <v>-19.2861096</v>
+        <v>-20.72260319999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1168361151599552</v>
+        <v>0.1187054866115329</v>
       </c>
       <c r="T63">
-        <v>1.347528855115822</v>
+        <v>1.382990140776764</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04825045890203483</v>
+        <v>0.0474722256939375</v>
       </c>
       <c r="W63">
-        <v>0.2244225417909002</v>
+        <v>0.2246060491813696</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2412522945101742</v>
+        <v>0.2373611284696875</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1843638354048316</v>
+        <v>0.1862638354048316</v>
       </c>
       <c r="C64">
-        <v>-304.4746081079026</v>
+        <v>-314.1280675723599</v>
       </c>
       <c r="D64">
-        <v>153.4553918920974</v>
+        <v>151.4169324276401</v>
       </c>
       <c r="E64">
-        <v>109.93</v>
+        <v>117.545</v>
       </c>
       <c r="F64">
-        <v>472.13</v>
+        <v>479.745</v>
       </c>
       <c r="G64">
         <v>14.2</v>
@@ -6535,37 +6535,37 @@
         <v>26.425</v>
       </c>
       <c r="M64">
-        <v>111.328254</v>
+        <v>113.123871</v>
       </c>
       <c r="N64">
-        <v>-84.903254</v>
+        <v>-86.69887100000001</v>
       </c>
       <c r="O64">
-        <v>-16.9806508</v>
+        <v>-17.3397742</v>
       </c>
       <c r="P64">
-        <v>-67.9226032</v>
+        <v>-69.3590968</v>
       </c>
       <c r="Q64">
-        <v>-20.72260319999999</v>
+        <v>-22.1590968</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1187054866115329</v>
+        <v>0.1206759051686014</v>
       </c>
       <c r="T64">
-        <v>1.382990140776764</v>
+        <v>1.42036825268965</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0474722256939375</v>
+        <v>0.04671869830197023</v>
       </c>
       <c r="W64">
-        <v>0.2246060491813696</v>
+        <v>0.2247837309403954</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2373611284696875</v>
+        <v>0.2335934915098511</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1862638354048316</v>
+        <v>0.1881638354048316</v>
       </c>
       <c r="C65">
-        <v>-314.1280675723599</v>
+        <v>-323.7280803319862</v>
       </c>
       <c r="D65">
-        <v>151.4169324276401</v>
+        <v>149.4319196680138</v>
       </c>
       <c r="E65">
-        <v>117.545</v>
+        <v>125.16</v>
       </c>
       <c r="F65">
-        <v>479.745</v>
+        <v>487.36</v>
       </c>
       <c r="G65">
         <v>14.2</v>
@@ -6617,37 +6617,37 @@
         <v>26.425</v>
       </c>
       <c r="M65">
-        <v>113.123871</v>
+        <v>114.919488</v>
       </c>
       <c r="N65">
-        <v>-86.69887100000001</v>
+        <v>-88.494488</v>
       </c>
       <c r="O65">
-        <v>-17.3397742</v>
+        <v>-17.6988976</v>
       </c>
       <c r="P65">
-        <v>-69.3590968</v>
+        <v>-70.79559040000001</v>
       </c>
       <c r="Q65">
-        <v>-22.1590968</v>
+        <v>-23.59559040000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1206759051686014</v>
+        <v>0.1227557914232848</v>
       </c>
       <c r="T65">
-        <v>1.42036825268965</v>
+        <v>1.459822926375474</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04671869830197023</v>
+        <v>0.04598871864100195</v>
       </c>
       <c r="W65">
-        <v>0.2247837309403954</v>
+        <v>0.2249558601444517</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2335934915098511</v>
+        <v>0.2299435932050097</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1881638354048316</v>
+        <v>0.1900638354048316</v>
       </c>
       <c r="C66">
-        <v>-323.7280803319862</v>
+        <v>-333.2767211790715</v>
       </c>
       <c r="D66">
-        <v>149.4319196680138</v>
+        <v>147.4982788209285</v>
       </c>
       <c r="E66">
-        <v>125.16</v>
+        <v>132.775</v>
       </c>
       <c r="F66">
-        <v>487.36</v>
+        <v>494.975</v>
       </c>
       <c r="G66">
         <v>14.2</v>
@@ -6699,37 +6699,37 @@
         <v>26.425</v>
       </c>
       <c r="M66">
-        <v>114.919488</v>
+        <v>116.715105</v>
       </c>
       <c r="N66">
-        <v>-88.494488</v>
+        <v>-90.29010500000001</v>
       </c>
       <c r="O66">
-        <v>-17.6988976</v>
+        <v>-18.058021</v>
       </c>
       <c r="P66">
-        <v>-70.79559040000001</v>
+        <v>-72.23208400000001</v>
       </c>
       <c r="Q66">
-        <v>-23.59559040000001</v>
+        <v>-25.03208400000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1227557914232848</v>
+        <v>0.1249545283210929</v>
       </c>
       <c r="T66">
-        <v>1.459822926375474</v>
+        <v>1.501532152843344</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04598871864100195</v>
+        <v>0.04528119989267884</v>
       </c>
       <c r="W66">
-        <v>0.2249558601444517</v>
+        <v>0.2251226930653063</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2299435932050097</v>
+        <v>0.2264059994633941</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1900638354048316</v>
+        <v>0.1919638354048317</v>
       </c>
       <c r="C67">
-        <v>-333.2767211790715</v>
+        <v>-342.7759588869913</v>
       </c>
       <c r="D67">
-        <v>147.4982788209285</v>
+        <v>145.6140411130087</v>
       </c>
       <c r="E67">
-        <v>132.775</v>
+        <v>140.39</v>
       </c>
       <c r="F67">
-        <v>494.975</v>
+        <v>502.59</v>
       </c>
       <c r="G67">
         <v>14.2</v>
@@ -6781,37 +6781,37 @@
         <v>26.425</v>
       </c>
       <c r="M67">
-        <v>116.715105</v>
+        <v>118.510722</v>
       </c>
       <c r="N67">
-        <v>-90.29010500000001</v>
+        <v>-92.08572200000002</v>
       </c>
       <c r="O67">
-        <v>-18.058021</v>
+        <v>-18.41714440000001</v>
       </c>
       <c r="P67">
-        <v>-72.23208400000001</v>
+        <v>-73.66857760000002</v>
       </c>
       <c r="Q67">
-        <v>-25.03208400000001</v>
+        <v>-26.46857760000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1249545283210929</v>
+        <v>0.127282602683478</v>
       </c>
       <c r="T67">
-        <v>1.501532152843344</v>
+        <v>1.54569486322109</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04528119989267884</v>
+        <v>0.04459512110642613</v>
       </c>
       <c r="W67">
-        <v>0.2251226930653063</v>
+        <v>0.2252844704431047</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2264059994633941</v>
+        <v>0.2229756055321306</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1919638354048317</v>
+        <v>0.1938638354048317</v>
       </c>
       <c r="C68">
-        <v>-342.7759588869913</v>
+        <v>-352.2276628965578</v>
       </c>
       <c r="D68">
-        <v>145.6140411130087</v>
+        <v>143.7773371034422</v>
       </c>
       <c r="E68">
-        <v>140.39</v>
+        <v>148.0050000000001</v>
       </c>
       <c r="F68">
-        <v>502.59</v>
+        <v>510.205</v>
       </c>
       <c r="G68">
         <v>14.2</v>
@@ -6863,37 +6863,37 @@
         <v>26.425</v>
       </c>
       <c r="M68">
-        <v>118.510722</v>
+        <v>120.306339</v>
       </c>
       <c r="N68">
-        <v>-92.08572200000002</v>
+        <v>-93.88133900000001</v>
       </c>
       <c r="O68">
-        <v>-18.41714440000001</v>
+        <v>-18.7762678</v>
       </c>
       <c r="P68">
-        <v>-73.66857760000002</v>
+        <v>-75.10507120000001</v>
       </c>
       <c r="Q68">
-        <v>-26.46857760000002</v>
+        <v>-27.90507120000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.127282602683478</v>
+        <v>0.1297517724617652</v>
       </c>
       <c r="T68">
-        <v>1.54569486322109</v>
+        <v>1.592534101500517</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04459512110642613</v>
+        <v>0.04392952228394215</v>
       </c>
       <c r="W68">
-        <v>0.2252844704431047</v>
+        <v>0.2254414186454465</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2229756055321306</v>
+        <v>0.2196476114197108</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1938638354048317</v>
+        <v>0.1957638354048317</v>
       </c>
       <c r="C69">
-        <v>-352.2276628965578</v>
+        <v>-361.6336095026478</v>
       </c>
       <c r="D69">
-        <v>143.7773371034422</v>
+        <v>141.9863904973523</v>
       </c>
       <c r="E69">
-        <v>148.0050000000001</v>
+        <v>155.6200000000001</v>
       </c>
       <c r="F69">
-        <v>510.205</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="G69">
         <v>14.2</v>
@@ -6945,37 +6945,37 @@
         <v>26.425</v>
       </c>
       <c r="M69">
-        <v>120.306339</v>
+        <v>122.101956</v>
       </c>
       <c r="N69">
-        <v>-93.88133900000001</v>
+        <v>-95.67695600000002</v>
       </c>
       <c r="O69">
-        <v>-18.7762678</v>
+        <v>-19.1353912</v>
       </c>
       <c r="P69">
-        <v>-75.10507120000001</v>
+        <v>-76.54156480000002</v>
       </c>
       <c r="Q69">
-        <v>-27.90507120000001</v>
+        <v>-29.34156480000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1297517724617652</v>
+        <v>0.1323752653511954</v>
       </c>
       <c r="T69">
-        <v>1.592534101500517</v>
+        <v>1.642300792172408</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04392952228394215</v>
+        <v>0.04328349989741359</v>
       </c>
       <c r="W69">
-        <v>0.2254414186454465</v>
+        <v>0.2255937507241899</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2196476114197108</v>
+        <v>0.2164174994870679</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1957638354048317</v>
+        <v>0.1976638354048317</v>
       </c>
       <c r="C70">
-        <v>-361.6336095026478</v>
+        <v>-370.9954875841372</v>
       </c>
       <c r="D70">
-        <v>141.9863904973523</v>
+        <v>140.2395124158629</v>
       </c>
       <c r="E70">
-        <v>155.6200000000001</v>
+        <v>163.2350000000001</v>
       </c>
       <c r="F70">
-        <v>517.8200000000001</v>
+        <v>525.4350000000001</v>
       </c>
       <c r="G70">
         <v>14.2</v>
@@ -7027,37 +7027,37 @@
         <v>26.425</v>
       </c>
       <c r="M70">
-        <v>122.101956</v>
+        <v>123.897573</v>
       </c>
       <c r="N70">
-        <v>-95.67695600000002</v>
+        <v>-97.47257300000003</v>
       </c>
       <c r="O70">
-        <v>-19.1353912</v>
+        <v>-19.49451460000001</v>
       </c>
       <c r="P70">
-        <v>-76.54156480000002</v>
+        <v>-77.97805840000002</v>
       </c>
       <c r="Q70">
-        <v>-29.34156480000001</v>
+        <v>-30.77805840000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1323752653511954</v>
+        <v>0.1351680158463952</v>
       </c>
       <c r="T70">
-        <v>1.642300792172408</v>
+        <v>1.695278237081195</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04328349989741359</v>
+        <v>0.04265620279745107</v>
       </c>
       <c r="W70">
-        <v>0.2255937507241899</v>
+        <v>0.2257416673803611</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2164174994870679</v>
+        <v>0.2132810139872554</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1976638354048317</v>
+        <v>0.1995638354048316</v>
       </c>
       <c r="C71">
-        <v>-370.9954875841372</v>
+        <v>-380.3149039160013</v>
       </c>
       <c r="D71">
-        <v>140.2395124158629</v>
+        <v>138.5350960839988</v>
       </c>
       <c r="E71">
-        <v>163.2350000000001</v>
+        <v>170.8500000000001</v>
       </c>
       <c r="F71">
-        <v>525.4350000000001</v>
+        <v>533.0500000000001</v>
       </c>
       <c r="G71">
         <v>14.2</v>
@@ -7109,37 +7109,37 @@
         <v>26.425</v>
       </c>
       <c r="M71">
-        <v>123.897573</v>
+        <v>125.69319</v>
       </c>
       <c r="N71">
-        <v>-97.47257300000003</v>
+        <v>-99.26819000000002</v>
       </c>
       <c r="O71">
-        <v>-19.49451460000001</v>
+        <v>-19.853638</v>
       </c>
       <c r="P71">
-        <v>-77.97805840000002</v>
+        <v>-79.41455200000001</v>
       </c>
       <c r="Q71">
-        <v>-30.77805840000002</v>
+        <v>-32.21455200000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1351680158463952</v>
+        <v>0.1381469497079417</v>
       </c>
       <c r="T71">
-        <v>1.695278237081195</v>
+        <v>1.751787511650569</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04265620279745107</v>
+        <v>0.04204682847177321</v>
       </c>
       <c r="W71">
-        <v>0.2257416673803611</v>
+        <v>0.2258853578463559</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2132810139872554</v>
+        <v>0.2102341423588661</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1995638354048316</v>
+        <v>0.2014638354048316</v>
       </c>
       <c r="C72">
-        <v>-380.3149039160013</v>
+        <v>-389.5933880987001</v>
       </c>
       <c r="D72">
-        <v>138.5350960839988</v>
+        <v>136.8716119013</v>
       </c>
       <c r="E72">
-        <v>170.8500000000001</v>
+        <v>178.4650000000001</v>
       </c>
       <c r="F72">
-        <v>533.0500000000001</v>
+        <v>540.6650000000001</v>
       </c>
       <c r="G72">
         <v>14.2</v>
@@ -7191,37 +7191,37 @@
         <v>26.425</v>
       </c>
       <c r="M72">
-        <v>125.69319</v>
+        <v>127.488807</v>
       </c>
       <c r="N72">
-        <v>-99.26819000000002</v>
+        <v>-101.063807</v>
       </c>
       <c r="O72">
-        <v>-19.853638</v>
+        <v>-20.21276140000001</v>
       </c>
       <c r="P72">
-        <v>-79.41455200000001</v>
+        <v>-80.85104560000002</v>
       </c>
       <c r="Q72">
-        <v>-32.21455200000001</v>
+        <v>-33.65104560000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1381469497079417</v>
+        <v>0.1413313272840777</v>
       </c>
       <c r="T72">
-        <v>1.751787511650569</v>
+        <v>1.812193977569554</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04204682847177321</v>
+        <v>0.04145461962005809</v>
       </c>
       <c r="W72">
-        <v>0.2258853578463559</v>
+        <v>0.2260250006935903</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2102341423588661</v>
+        <v>0.2072730981002904</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2014638354048316</v>
+        <v>0.2033638354048316</v>
       </c>
       <c r="C73">
-        <v>-389.5933880987001</v>
+        <v>-398.8323971366316</v>
       </c>
       <c r="D73">
-        <v>136.8716119012999</v>
+        <v>135.2476028633683</v>
       </c>
       <c r="E73">
-        <v>178.465</v>
+        <v>186.08</v>
       </c>
       <c r="F73">
-        <v>540.665</v>
+        <v>548.28</v>
       </c>
       <c r="G73">
         <v>14.2</v>
@@ -7273,37 +7273,37 @@
         <v>26.425</v>
       </c>
       <c r="M73">
-        <v>127.488807</v>
+        <v>129.284424</v>
       </c>
       <c r="N73">
-        <v>-101.063807</v>
+        <v>-102.859424</v>
       </c>
       <c r="O73">
-        <v>-20.2127614</v>
+        <v>-20.5718848</v>
       </c>
       <c r="P73">
-        <v>-80.85104559999999</v>
+        <v>-82.2875392</v>
       </c>
       <c r="Q73">
-        <v>-33.65104559999999</v>
+        <v>-35.08753919999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1413313272840776</v>
+        <v>0.1447431604013661</v>
       </c>
       <c r="T73">
-        <v>1.812193977569553</v>
+        <v>1.87691519105418</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04145461962005809</v>
+        <v>0.04087886101422395</v>
       </c>
       <c r="W73">
-        <v>0.2260250006935903</v>
+        <v>0.226160764572846</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2072730981002905</v>
+        <v>0.2043943050711198</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2033638354048316</v>
+        <v>0.2052638354048316</v>
       </c>
       <c r="C74">
-        <v>-398.8323971366316</v>
+        <v>-408.0333196944651</v>
       </c>
       <c r="D74">
-        <v>135.2476028633683</v>
+        <v>133.6616803055348</v>
       </c>
       <c r="E74">
-        <v>186.08</v>
+        <v>193.695</v>
       </c>
       <c r="F74">
-        <v>548.28</v>
+        <v>555.895</v>
       </c>
       <c r="G74">
         <v>14.2</v>
@@ -7355,37 +7355,37 @@
         <v>26.425</v>
       </c>
       <c r="M74">
-        <v>129.284424</v>
+        <v>131.080041</v>
       </c>
       <c r="N74">
-        <v>-102.859424</v>
+        <v>-104.655041</v>
       </c>
       <c r="O74">
-        <v>-20.5718848</v>
+        <v>-20.9310082</v>
       </c>
       <c r="P74">
-        <v>-82.2875392</v>
+        <v>-83.7240328</v>
       </c>
       <c r="Q74">
-        <v>-35.08753919999999</v>
+        <v>-36.5240328</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1447431604013661</v>
+        <v>0.148407721897713</v>
       </c>
       <c r="T74">
-        <v>1.87691519105418</v>
+        <v>1.946430568500631</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04087886101422395</v>
+        <v>0.04031887661676883</v>
       </c>
       <c r="W74">
-        <v>0.226160764572846</v>
+        <v>0.2262928088937659</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2043943050711198</v>
+        <v>0.2015943830838441</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2052638354048316</v>
+        <v>0.2071638354048317</v>
       </c>
       <c r="C75">
-        <v>-408.0333196944651</v>
+        <v>-417.1974800574827</v>
       </c>
       <c r="D75">
-        <v>133.6616803055348</v>
+        <v>132.1125199425173</v>
       </c>
       <c r="E75">
-        <v>193.695</v>
+        <v>201.31</v>
       </c>
       <c r="F75">
-        <v>555.895</v>
+        <v>563.51</v>
       </c>
       <c r="G75">
         <v>14.2</v>
@@ -7437,37 +7437,37 @@
         <v>26.425</v>
       </c>
       <c r="M75">
-        <v>131.080041</v>
+        <v>132.875658</v>
       </c>
       <c r="N75">
-        <v>-104.655041</v>
+        <v>-106.450658</v>
       </c>
       <c r="O75">
-        <v>-20.9310082</v>
+        <v>-21.29013160000001</v>
       </c>
       <c r="P75">
-        <v>-83.7240328</v>
+        <v>-85.16052640000001</v>
       </c>
       <c r="Q75">
-        <v>-36.5240328</v>
+        <v>-37.96052640000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.148407721897713</v>
+        <v>0.1523541727399327</v>
       </c>
       <c r="T75">
-        <v>1.946430568500631</v>
+        <v>2.021293282673732</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04031887661676883</v>
+        <v>0.03977402693275844</v>
       </c>
       <c r="W75">
-        <v>0.2262928088937659</v>
+        <v>0.2264212844492556</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2015943830838441</v>
+        <v>0.1988701346637922</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2071638354048317</v>
+        <v>0.2090638354048316</v>
       </c>
       <c r="C76">
-        <v>-417.1974800574827</v>
+        <v>-426.3261418196709</v>
       </c>
       <c r="D76">
-        <v>132.1125199425173</v>
+        <v>130.5988581803292</v>
       </c>
       <c r="E76">
-        <v>201.31</v>
+        <v>208.925</v>
       </c>
       <c r="F76">
-        <v>563.51</v>
+        <v>571.125</v>
       </c>
       <c r="G76">
         <v>14.2</v>
@@ -7519,37 +7519,37 @@
         <v>26.425</v>
       </c>
       <c r="M76">
-        <v>132.875658</v>
+        <v>134.671275</v>
       </c>
       <c r="N76">
-        <v>-106.450658</v>
+        <v>-108.246275</v>
       </c>
       <c r="O76">
-        <v>-21.29013160000001</v>
+        <v>-21.649255</v>
       </c>
       <c r="P76">
-        <v>-85.16052640000001</v>
+        <v>-86.59702000000001</v>
       </c>
       <c r="Q76">
-        <v>-37.96052640000001</v>
+        <v>-39.39702000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1523541727399327</v>
+        <v>0.1566163396495301</v>
       </c>
       <c r="T76">
-        <v>2.021293282673732</v>
+        <v>2.102145013980682</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03977402693275844</v>
+        <v>0.03924370657365499</v>
       </c>
       <c r="W76">
-        <v>0.2264212844492556</v>
+        <v>0.2265463339899322</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1988701346637922</v>
+        <v>0.196218532868275</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2090638354048316</v>
+        <v>0.2109638354048317</v>
       </c>
       <c r="C77">
-        <v>-426.3261418196709</v>
+        <v>-435.4205113211497</v>
       </c>
       <c r="D77">
-        <v>130.5988581803292</v>
+        <v>129.1194886788504</v>
       </c>
       <c r="E77">
-        <v>208.925</v>
+        <v>216.54</v>
       </c>
       <c r="F77">
-        <v>571.125</v>
+        <v>578.74</v>
       </c>
       <c r="G77">
         <v>14.2</v>
@@ -7601,37 +7601,37 @@
         <v>26.425</v>
       </c>
       <c r="M77">
-        <v>134.671275</v>
+        <v>136.466892</v>
       </c>
       <c r="N77">
-        <v>-108.246275</v>
+        <v>-110.041892</v>
       </c>
       <c r="O77">
-        <v>-21.649255</v>
+        <v>-22.0083784</v>
       </c>
       <c r="P77">
-        <v>-86.59702000000001</v>
+        <v>-88.03351360000001</v>
       </c>
       <c r="Q77">
-        <v>-39.39702000000001</v>
+        <v>-40.8335136</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1566163396495301</v>
+        <v>0.1612336871349271</v>
       </c>
       <c r="T77">
-        <v>2.102145013980682</v>
+        <v>2.18973438956321</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03924370657365499</v>
+        <v>0.03872734201347533</v>
       </c>
       <c r="W77">
-        <v>0.2265463339899322</v>
+        <v>0.2266680927532225</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.196218532868275</v>
+        <v>0.1936367100673766</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2109638354048317</v>
+        <v>0.2128638354048316</v>
       </c>
       <c r="C78">
-        <v>-435.4205113211497</v>
+        <v>-444.4817408545911</v>
       </c>
       <c r="D78">
-        <v>129.1194886788504</v>
+        <v>127.6732591454089</v>
       </c>
       <c r="E78">
-        <v>216.54</v>
+        <v>224.155</v>
       </c>
       <c r="F78">
-        <v>578.74</v>
+        <v>586.355</v>
       </c>
       <c r="G78">
         <v>14.2</v>
@@ -7683,37 +7683,37 @@
         <v>26.425</v>
       </c>
       <c r="M78">
-        <v>136.466892</v>
+        <v>138.262509</v>
       </c>
       <c r="N78">
-        <v>-110.041892</v>
+        <v>-111.837509</v>
       </c>
       <c r="O78">
-        <v>-22.0083784</v>
+        <v>-22.36750180000001</v>
       </c>
       <c r="P78">
-        <v>-88.03351360000001</v>
+        <v>-89.47000720000003</v>
       </c>
       <c r="Q78">
-        <v>-40.8335136</v>
+        <v>-42.27000720000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1612336871349271</v>
+        <v>0.1662525430973153</v>
       </c>
       <c r="T78">
-        <v>2.18973438956321</v>
+        <v>2.284940232587698</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03872734201347533</v>
+        <v>0.03822438951979382</v>
       </c>
       <c r="W78">
-        <v>0.2266680927532225</v>
+        <v>0.2267866889512326</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1936367100673766</v>
+        <v>0.1911219475989691</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2128638354048316</v>
+        <v>0.2147638354048316</v>
       </c>
       <c r="C79">
-        <v>-444.4817408545911</v>
+        <v>-453.5109316585399</v>
       </c>
       <c r="D79">
-        <v>127.6732591454089</v>
+        <v>126.2590683414601</v>
       </c>
       <c r="E79">
-        <v>224.155</v>
+        <v>231.77</v>
       </c>
       <c r="F79">
-        <v>586.355</v>
+        <v>593.97</v>
       </c>
       <c r="G79">
         <v>14.2</v>
@@ -7765,37 +7765,37 @@
         <v>26.425</v>
       </c>
       <c r="M79">
-        <v>138.262509</v>
+        <v>140.058126</v>
       </c>
       <c r="N79">
-        <v>-111.837509</v>
+        <v>-113.633126</v>
       </c>
       <c r="O79">
-        <v>-22.36750180000001</v>
+        <v>-22.7266252</v>
       </c>
       <c r="P79">
-        <v>-89.47000720000003</v>
+        <v>-90.90650080000002</v>
       </c>
       <c r="Q79">
-        <v>-42.27000720000002</v>
+        <v>-43.70650080000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1662525430973153</v>
+        <v>0.1717276586926478</v>
       </c>
       <c r="T79">
-        <v>2.284940232587698</v>
+        <v>2.388801152250775</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03822438951979382</v>
+        <v>0.03773433324389903</v>
       </c>
       <c r="W79">
-        <v>0.2267866889512326</v>
+        <v>0.2269022442210886</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1911219475989691</v>
+        <v>0.1886716662194952</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2147638354048316</v>
+        <v>0.2166638354048316</v>
       </c>
       <c r="C80">
-        <v>-453.5109316585399</v>
+        <v>-462.5091367139787</v>
       </c>
       <c r="D80">
-        <v>126.2590683414601</v>
+        <v>124.8758632860213</v>
       </c>
       <c r="E80">
-        <v>231.77</v>
+        <v>239.385</v>
       </c>
       <c r="F80">
-        <v>593.97</v>
+        <v>601.585</v>
       </c>
       <c r="G80">
         <v>14.2</v>
@@ -7847,37 +7847,37 @@
         <v>26.425</v>
       </c>
       <c r="M80">
-        <v>140.058126</v>
+        <v>141.853743</v>
       </c>
       <c r="N80">
-        <v>-113.633126</v>
+        <v>-115.428743</v>
       </c>
       <c r="O80">
-        <v>-22.7266252</v>
+        <v>-23.0857486</v>
       </c>
       <c r="P80">
-        <v>-90.90650080000002</v>
+        <v>-92.34299440000001</v>
       </c>
       <c r="Q80">
-        <v>-43.70650080000001</v>
+        <v>-45.14299440000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1717276586926478</v>
+        <v>0.1777242138684882</v>
       </c>
       <c r="T80">
-        <v>2.388801152250775</v>
+        <v>2.502553588072241</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03773433324389903</v>
+        <v>0.03725668345600158</v>
       </c>
       <c r="W80">
-        <v>0.2269022442210886</v>
+        <v>0.2270148740410748</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1886716662194952</v>
+        <v>0.1862834172800079</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2166638354048316</v>
+        <v>0.2185638354048317</v>
       </c>
       <c r="C81">
-        <v>-462.5091367139787</v>
+        <v>-471.4773633590606</v>
       </c>
       <c r="D81">
-        <v>124.8758632860213</v>
+        <v>123.5226366409394</v>
       </c>
       <c r="E81">
-        <v>239.385</v>
+        <v>247.0000000000001</v>
       </c>
       <c r="F81">
-        <v>601.585</v>
+        <v>609.2</v>
       </c>
       <c r="G81">
         <v>14.2</v>
@@ -7929,37 +7929,37 @@
         <v>26.425</v>
       </c>
       <c r="M81">
-        <v>141.853743</v>
+        <v>143.64936</v>
       </c>
       <c r="N81">
-        <v>-115.428743</v>
+        <v>-117.22436</v>
       </c>
       <c r="O81">
-        <v>-23.0857486</v>
+        <v>-23.44487200000001</v>
       </c>
       <c r="P81">
-        <v>-92.34299440000001</v>
+        <v>-93.77948800000003</v>
       </c>
       <c r="Q81">
-        <v>-45.14299440000001</v>
+        <v>-46.57948800000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1777242138684882</v>
+        <v>0.1843204245619126</v>
       </c>
       <c r="T81">
-        <v>2.502553588072241</v>
+        <v>2.627681267475853</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03725668345600158</v>
+        <v>0.03679097491280155</v>
       </c>
       <c r="W81">
-        <v>0.2270148740410748</v>
+        <v>0.2271246881155614</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1862834172800079</v>
+        <v>0.1839548745640077</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2185638354048317</v>
+        <v>0.2204638354048316</v>
       </c>
       <c r="C82">
-        <v>-471.4773633590606</v>
+        <v>-480.4165757356573</v>
       </c>
       <c r="D82">
-        <v>123.5226366409394</v>
+        <v>122.1984242643428</v>
       </c>
       <c r="E82">
-        <v>247.0000000000001</v>
+        <v>254.6150000000001</v>
       </c>
       <c r="F82">
-        <v>609.2</v>
+        <v>616.8150000000001</v>
       </c>
       <c r="G82">
         <v>14.2</v>
@@ -8011,37 +8011,37 @@
         <v>26.425</v>
       </c>
       <c r="M82">
-        <v>143.64936</v>
+        <v>145.444977</v>
       </c>
       <c r="N82">
-        <v>-117.22436</v>
+        <v>-119.019977</v>
       </c>
       <c r="O82">
-        <v>-23.44487200000001</v>
+        <v>-23.80399540000001</v>
       </c>
       <c r="P82">
-        <v>-93.77948800000003</v>
+        <v>-95.21598160000002</v>
       </c>
       <c r="Q82">
-        <v>-46.57948800000003</v>
+        <v>-48.01598160000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1843204245619126</v>
+        <v>0.1916109732230659</v>
       </c>
       <c r="T82">
-        <v>2.627681267475853</v>
+        <v>2.76598028155353</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03679097491280155</v>
+        <v>0.03633676534597684</v>
       </c>
       <c r="W82">
-        <v>0.2271246881155614</v>
+        <v>0.2272317907314187</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1839548745640077</v>
+        <v>0.1816838267298843</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2204638354048316</v>
+        <v>0.2223638354048317</v>
       </c>
       <c r="C83">
-        <v>-480.4165757356573</v>
+        <v>-489.3276970802071</v>
       </c>
       <c r="D83">
-        <v>122.1984242643428</v>
+        <v>120.902302919793</v>
       </c>
       <c r="E83">
-        <v>254.6150000000001</v>
+        <v>262.2300000000001</v>
       </c>
       <c r="F83">
-        <v>616.8150000000001</v>
+        <v>624.4300000000001</v>
       </c>
       <c r="G83">
         <v>14.2</v>
@@ -8093,37 +8093,37 @@
         <v>26.425</v>
       </c>
       <c r="M83">
-        <v>145.444977</v>
+        <v>147.240594</v>
       </c>
       <c r="N83">
-        <v>-119.019977</v>
+        <v>-120.815594</v>
       </c>
       <c r="O83">
-        <v>-23.80399540000001</v>
+        <v>-24.16311880000001</v>
       </c>
       <c r="P83">
-        <v>-95.21598160000002</v>
+        <v>-96.65247520000001</v>
       </c>
       <c r="Q83">
-        <v>-48.01598160000002</v>
+        <v>-49.45247520000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1916109732230659</v>
+        <v>0.1997115828465696</v>
       </c>
       <c r="T83">
-        <v>2.76598028155353</v>
+        <v>2.919645852750948</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03633676534597684</v>
+        <v>0.03589363406126981</v>
       </c>
       <c r="W83">
-        <v>0.2272317907314187</v>
+        <v>0.2273362810883526</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1816838267298843</v>
+        <v>0.179468170306349</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2223638354048317</v>
+        <v>0.2242638354048317</v>
       </c>
       <c r="C84">
-        <v>-489.3276970802071</v>
+        <v>-498.2116118703055</v>
       </c>
       <c r="D84">
-        <v>120.902302919793</v>
+        <v>119.6333881296946</v>
       </c>
       <c r="E84">
-        <v>262.2300000000001</v>
+        <v>269.8450000000001</v>
       </c>
       <c r="F84">
-        <v>624.4300000000001</v>
+        <v>632.0450000000001</v>
       </c>
       <c r="G84">
         <v>14.2</v>
@@ -8175,37 +8175,37 @@
         <v>26.425</v>
       </c>
       <c r="M84">
-        <v>147.240594</v>
+        <v>149.036211</v>
       </c>
       <c r="N84">
-        <v>-120.815594</v>
+        <v>-122.611211</v>
       </c>
       <c r="O84">
-        <v>-24.16311880000001</v>
+        <v>-24.52224220000001</v>
       </c>
       <c r="P84">
-        <v>-96.65247520000001</v>
+        <v>-98.08896880000003</v>
       </c>
       <c r="Q84">
-        <v>-49.45247520000001</v>
+        <v>-50.88896880000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1997115828465696</v>
+        <v>0.208765205366956</v>
       </c>
       <c r="T84">
-        <v>2.919645852750948</v>
+        <v>3.09138972644218</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03589363406126981</v>
+        <v>0.03546118063884487</v>
       </c>
       <c r="W84">
-        <v>0.2273362810883526</v>
+        <v>0.2274382536053604</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.179468170306349</v>
+        <v>0.1773059031942243</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2242638354048317</v>
+        <v>0.2261638354048316</v>
       </c>
       <c r="C85">
-        <v>-498.2116118703055</v>
+        <v>-507.0691678375204</v>
       </c>
       <c r="D85">
-        <v>119.6333881296946</v>
+        <v>118.3908321624798</v>
       </c>
       <c r="E85">
-        <v>269.8450000000001</v>
+        <v>277.4600000000001</v>
       </c>
       <c r="F85">
-        <v>632.0450000000001</v>
+        <v>639.6600000000001</v>
       </c>
       <c r="G85">
         <v>14.2</v>
@@ -8257,37 +8257,37 @@
         <v>26.425</v>
       </c>
       <c r="M85">
-        <v>149.036211</v>
+        <v>150.831828</v>
       </c>
       <c r="N85">
-        <v>-122.611211</v>
+        <v>-124.406828</v>
       </c>
       <c r="O85">
-        <v>-24.52224220000001</v>
+        <v>-24.88136560000001</v>
       </c>
       <c r="P85">
-        <v>-98.08896880000003</v>
+        <v>-99.52546240000002</v>
       </c>
       <c r="Q85">
-        <v>-50.88896880000003</v>
+        <v>-52.32546240000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.208765205366956</v>
+        <v>0.2189505307023908</v>
       </c>
       <c r="T85">
-        <v>3.09138972644218</v>
+        <v>3.284601584344817</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03546118063884487</v>
+        <v>0.03503902372647767</v>
       </c>
       <c r="W85">
-        <v>0.2274382536053604</v>
+        <v>0.2275377982052966</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1773059031942243</v>
+        <v>0.1751951186323883</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2261638354048316</v>
+        <v>0.2280638354048316</v>
       </c>
       <c r="C86">
-        <v>-507.0691678375202</v>
+        <v>-515.9011778560654</v>
       </c>
       <c r="D86">
-        <v>118.3908321624798</v>
+        <v>117.1738221439346</v>
       </c>
       <c r="E86">
-        <v>277.46</v>
+        <v>285.075</v>
       </c>
       <c r="F86">
-        <v>639.66</v>
+        <v>647.275</v>
       </c>
       <c r="G86">
         <v>14.2</v>
@@ -8339,37 +8339,37 @@
         <v>26.425</v>
       </c>
       <c r="M86">
-        <v>150.831828</v>
+        <v>152.627445</v>
       </c>
       <c r="N86">
-        <v>-124.406828</v>
+        <v>-126.202445</v>
       </c>
       <c r="O86">
-        <v>-24.8813656</v>
+        <v>-25.240489</v>
       </c>
       <c r="P86">
-        <v>-99.52546240000001</v>
+        <v>-100.961956</v>
       </c>
       <c r="Q86">
-        <v>-52.32546240000001</v>
+        <v>-53.761956</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2189505307023907</v>
+        <v>0.2304938994158834</v>
       </c>
       <c r="T86">
-        <v>3.284601584344815</v>
+        <v>3.503575023301136</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03503902372647768</v>
+        <v>0.03462679991793088</v>
       </c>
       <c r="W86">
-        <v>0.2275377982052966</v>
+        <v>0.2276350005793519</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1751951186323883</v>
+        <v>0.1731339995896544</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2280638354048316</v>
+        <v>0.2299638354048316</v>
       </c>
       <c r="C87">
-        <v>-515.9011778560654</v>
+        <v>-524.7084217161673</v>
       </c>
       <c r="D87">
-        <v>117.1738221439346</v>
+        <v>115.9815782838326</v>
       </c>
       <c r="E87">
-        <v>285.075</v>
+        <v>292.69</v>
       </c>
       <c r="F87">
-        <v>647.275</v>
+        <v>654.89</v>
       </c>
       <c r="G87">
         <v>14.2</v>
@@ -8421,37 +8421,37 @@
         <v>26.425</v>
       </c>
       <c r="M87">
-        <v>152.627445</v>
+        <v>154.423062</v>
       </c>
       <c r="N87">
-        <v>-126.202445</v>
+        <v>-127.998062</v>
       </c>
       <c r="O87">
-        <v>-25.240489</v>
+        <v>-25.59961240000001</v>
       </c>
       <c r="P87">
-        <v>-100.961956</v>
+        <v>-102.3984496</v>
       </c>
       <c r="Q87">
-        <v>-53.761956</v>
+        <v>-55.19844960000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2304938994158834</v>
+        <v>0.2436863208027323</v>
       </c>
       <c r="T87">
-        <v>3.503575023301136</v>
+        <v>3.75383038210836</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03462679991793088</v>
+        <v>0.03422416270958284</v>
       </c>
       <c r="W87">
-        <v>0.2276350005793519</v>
+        <v>0.2277299424330804</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1731339995896544</v>
+        <v>0.1711208135479142</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2299638354048316</v>
+        <v>0.2318638354048316</v>
       </c>
       <c r="C88">
-        <v>-524.7084217161673</v>
+        <v>-533.4916477902614</v>
       </c>
       <c r="D88">
-        <v>115.9815782838326</v>
+        <v>114.8133522097386</v>
       </c>
       <c r="E88">
-        <v>292.69</v>
+        <v>300.305</v>
       </c>
       <c r="F88">
-        <v>654.89</v>
+        <v>662.505</v>
       </c>
       <c r="G88">
         <v>14.2</v>
@@ -8503,37 +8503,37 @@
         <v>26.425</v>
       </c>
       <c r="M88">
-        <v>154.423062</v>
+        <v>156.218679</v>
       </c>
       <c r="N88">
-        <v>-127.998062</v>
+        <v>-129.793679</v>
       </c>
       <c r="O88">
-        <v>-25.59961240000001</v>
+        <v>-25.9587358</v>
       </c>
       <c r="P88">
-        <v>-102.3984496</v>
+        <v>-103.8349432</v>
       </c>
       <c r="Q88">
-        <v>-55.19844960000002</v>
+        <v>-56.6349432</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2436863208027323</v>
+        <v>0.2589083454798655</v>
       </c>
       <c r="T88">
-        <v>3.75383038210836</v>
+        <v>4.042586565347465</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03422416270958284</v>
+        <v>0.03383078152901293</v>
       </c>
       <c r="W88">
-        <v>0.2277299424330804</v>
+        <v>0.2278227017154587</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1711208135479142</v>
+        <v>0.1691539076450647</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2318638354048316</v>
+        <v>0.2337638354048316</v>
       </c>
       <c r="C89">
-        <v>-533.4916477902614</v>
+        <v>-542.2515745994922</v>
       </c>
       <c r="D89">
-        <v>114.8133522097386</v>
+        <v>113.6684254005078</v>
       </c>
       <c r="E89">
-        <v>300.305</v>
+        <v>307.92</v>
       </c>
       <c r="F89">
-        <v>662.505</v>
+        <v>670.12</v>
       </c>
       <c r="G89">
         <v>14.2</v>
@@ -8585,37 +8585,37 @@
         <v>26.425</v>
       </c>
       <c r="M89">
-        <v>156.218679</v>
+        <v>158.014296</v>
       </c>
       <c r="N89">
-        <v>-129.793679</v>
+        <v>-131.589296</v>
       </c>
       <c r="O89">
-        <v>-25.9587358</v>
+        <v>-26.3178592</v>
       </c>
       <c r="P89">
-        <v>-103.8349432</v>
+        <v>-105.2714368</v>
       </c>
       <c r="Q89">
-        <v>-56.6349432</v>
+        <v>-58.07143679999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2589083454798655</v>
+        <v>0.2766673742698543</v>
       </c>
       <c r="T89">
-        <v>4.042586565347465</v>
+        <v>4.37946877912642</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03383078152901293</v>
+        <v>0.0334463408298196</v>
       </c>
       <c r="W89">
-        <v>0.2278227017154587</v>
+        <v>0.2279133528323286</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1691539076450647</v>
+        <v>0.167231704149098</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2337638354048316</v>
+        <v>0.2356638354048316</v>
       </c>
       <c r="C90">
-        <v>-542.2515745994922</v>
+        <v>-550.9888922874154</v>
       </c>
       <c r="D90">
-        <v>113.6684254005078</v>
+        <v>112.5461077125846</v>
       </c>
       <c r="E90">
-        <v>307.92</v>
+        <v>315.535</v>
       </c>
       <c r="F90">
-        <v>670.12</v>
+        <v>677.735</v>
       </c>
       <c r="G90">
         <v>14.2</v>
@@ -8667,37 +8667,37 @@
         <v>26.425</v>
       </c>
       <c r="M90">
-        <v>158.014296</v>
+        <v>159.809913</v>
       </c>
       <c r="N90">
-        <v>-131.589296</v>
+        <v>-133.384913</v>
       </c>
       <c r="O90">
-        <v>-26.3178592</v>
+        <v>-26.67698260000001</v>
       </c>
       <c r="P90">
-        <v>-105.2714368</v>
+        <v>-106.7079304</v>
       </c>
       <c r="Q90">
-        <v>-58.07143679999999</v>
+        <v>-59.50793040000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2766673742698543</v>
+        <v>0.2976553173852956</v>
       </c>
       <c r="T90">
-        <v>4.37946877912642</v>
+        <v>4.77760230450155</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0334463408298196</v>
+        <v>0.03307053924746207</v>
       </c>
       <c r="W90">
-        <v>0.2279133528323286</v>
+        <v>0.2280019668454485</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.167231704149098</v>
+        <v>0.1653526962373103</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2356638354048316</v>
+        <v>0.2375638354048316</v>
       </c>
       <c r="C91">
-        <v>-550.9888922874154</v>
+        <v>-559.704264007245</v>
       </c>
       <c r="D91">
-        <v>112.5461077125846</v>
+        <v>111.445735992755</v>
       </c>
       <c r="E91">
-        <v>315.535</v>
+        <v>323.15</v>
       </c>
       <c r="F91">
-        <v>677.735</v>
+        <v>685.35</v>
       </c>
       <c r="G91">
         <v>14.2</v>
@@ -8749,37 +8749,37 @@
         <v>26.425</v>
       </c>
       <c r="M91">
-        <v>159.809913</v>
+        <v>161.60553</v>
       </c>
       <c r="N91">
-        <v>-133.384913</v>
+        <v>-135.18053</v>
       </c>
       <c r="O91">
-        <v>-26.67698260000001</v>
+        <v>-27.03610600000001</v>
       </c>
       <c r="P91">
-        <v>-106.7079304</v>
+        <v>-108.144424</v>
       </c>
       <c r="Q91">
-        <v>-59.50793040000003</v>
+        <v>-60.94442400000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2976553173852956</v>
+        <v>0.3228408491238252</v>
       </c>
       <c r="T91">
-        <v>4.77760230450155</v>
+        <v>5.255362534951706</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03307053924746207</v>
+        <v>0.03270308881137916</v>
       </c>
       <c r="W91">
-        <v>0.2280019668454485</v>
+        <v>0.2280886116582768</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1653526962373103</v>
+        <v>0.1635154440568957</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2375638354048316</v>
+        <v>0.2394638354048316</v>
       </c>
       <c r="C92">
-        <v>-559.704264007245</v>
+        <v>-568.3983272285121</v>
       </c>
       <c r="D92">
-        <v>111.445735992755</v>
+        <v>110.3666727714879</v>
       </c>
       <c r="E92">
-        <v>323.15</v>
+        <v>330.765</v>
       </c>
       <c r="F92">
-        <v>685.35</v>
+        <v>692.965</v>
       </c>
       <c r="G92">
         <v>14.2</v>
@@ -8831,37 +8831,37 @@
         <v>26.425</v>
       </c>
       <c r="M92">
-        <v>161.60553</v>
+        <v>163.401147</v>
       </c>
       <c r="N92">
-        <v>-135.18053</v>
+        <v>-136.976147</v>
       </c>
       <c r="O92">
-        <v>-27.03610600000001</v>
+        <v>-27.39522940000001</v>
       </c>
       <c r="P92">
-        <v>-108.144424</v>
+        <v>-109.5809176</v>
       </c>
       <c r="Q92">
-        <v>-60.94442400000003</v>
+        <v>-62.38091760000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3228408491238252</v>
+        <v>0.3536231656931391</v>
       </c>
       <c r="T92">
-        <v>5.255362534951706</v>
+        <v>5.839291705501895</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03270308881137916</v>
+        <v>0.03234371420905632</v>
       </c>
       <c r="W92">
-        <v>0.2280886116582768</v>
+        <v>0.2281733521895045</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1635154440568957</v>
+        <v>0.1617185710452814</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2394638354048316</v>
+        <v>0.2413638354048317</v>
       </c>
       <c r="C93">
-        <v>-568.3983272285121</v>
+        <v>-577.0716949685411</v>
       </c>
       <c r="D93">
-        <v>110.3666727714879</v>
+        <v>109.3083050314589</v>
       </c>
       <c r="E93">
-        <v>330.765</v>
+        <v>338.3800000000001</v>
       </c>
       <c r="F93">
-        <v>692.965</v>
+        <v>700.58</v>
       </c>
       <c r="G93">
         <v>14.2</v>
@@ -8913,37 +8913,37 @@
         <v>26.425</v>
       </c>
       <c r="M93">
-        <v>163.401147</v>
+        <v>165.196764</v>
       </c>
       <c r="N93">
-        <v>-136.976147</v>
+        <v>-138.771764</v>
       </c>
       <c r="O93">
-        <v>-27.39522940000001</v>
+        <v>-27.75435280000001</v>
       </c>
       <c r="P93">
-        <v>-109.5809176</v>
+        <v>-111.0174112</v>
       </c>
       <c r="Q93">
-        <v>-62.38091760000002</v>
+        <v>-63.81741120000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3536231656931391</v>
+        <v>0.3921010614047816</v>
       </c>
       <c r="T93">
-        <v>5.839291705501895</v>
+        <v>6.569203168689635</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03234371420905632</v>
+        <v>0.0319921520980883</v>
       </c>
       <c r="W93">
-        <v>0.2281733521895045</v>
+        <v>0.2282562505352708</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1617185710452814</v>
+        <v>0.1599607604904416</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2413638354048317</v>
+        <v>0.2432638354048316</v>
       </c>
       <c r="C94">
-        <v>-577.0716949685411</v>
+        <v>-585.7249569537416</v>
       </c>
       <c r="D94">
-        <v>109.3083050314589</v>
+        <v>108.2700430462584</v>
       </c>
       <c r="E94">
-        <v>338.3800000000001</v>
+        <v>345.9950000000001</v>
       </c>
       <c r="F94">
-        <v>700.58</v>
+        <v>708.1950000000001</v>
       </c>
       <c r="G94">
         <v>14.2</v>
@@ -8995,37 +8995,37 @@
         <v>26.425</v>
       </c>
       <c r="M94">
-        <v>165.196764</v>
+        <v>166.992381</v>
       </c>
       <c r="N94">
-        <v>-138.771764</v>
+        <v>-140.567381</v>
       </c>
       <c r="O94">
-        <v>-27.75435280000001</v>
+        <v>-28.1134762</v>
       </c>
       <c r="P94">
-        <v>-111.0174112</v>
+        <v>-112.4539048</v>
       </c>
       <c r="Q94">
-        <v>-63.81741120000001</v>
+        <v>-65.2539048</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3921010614047816</v>
+        <v>0.4415726416054647</v>
       </c>
       <c r="T94">
-        <v>6.569203168689635</v>
+        <v>7.507660764216725</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0319921520980883</v>
+        <v>0.03164815046262499</v>
       </c>
       <c r="W94">
-        <v>0.2282562505352708</v>
+        <v>0.228337366120913</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1599607604904416</v>
+        <v>0.1582407523131251</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2432638354048316</v>
+        <v>0.2451638354048317</v>
       </c>
       <c r="C95">
-        <v>-585.7249569537416</v>
+        <v>-594.3586807153424</v>
       </c>
       <c r="D95">
-        <v>108.2700430462584</v>
+        <v>107.2513192846576</v>
       </c>
       <c r="E95">
-        <v>345.9950000000001</v>
+        <v>353.6100000000001</v>
       </c>
       <c r="F95">
-        <v>708.1950000000001</v>
+        <v>715.8100000000001</v>
       </c>
       <c r="G95">
         <v>14.2</v>
@@ -9077,37 +9077,37 @@
         <v>26.425</v>
       </c>
       <c r="M95">
-        <v>166.992381</v>
+        <v>168.787998</v>
       </c>
       <c r="N95">
-        <v>-140.567381</v>
+        <v>-142.362998</v>
       </c>
       <c r="O95">
-        <v>-28.1134762</v>
+        <v>-28.4725996</v>
       </c>
       <c r="P95">
-        <v>-112.4539048</v>
+        <v>-113.8903984</v>
       </c>
       <c r="Q95">
-        <v>-65.2539048</v>
+        <v>-66.69039840000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4415726416054647</v>
+        <v>0.507534748539709</v>
       </c>
       <c r="T95">
-        <v>7.507660764216725</v>
+        <v>8.75893755825285</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03164815046262499</v>
+        <v>0.03131146801089494</v>
       </c>
       <c r="W95">
-        <v>0.228337366120913</v>
+        <v>0.228416755843031</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1582407523131251</v>
+        <v>0.1565573400544747</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2451638354048317</v>
+        <v>0.2470638354048316</v>
       </c>
       <c r="C96">
-        <v>-594.3586807153424</v>
+        <v>-602.9734126238413</v>
       </c>
       <c r="D96">
-        <v>107.2513192846576</v>
+        <v>106.2515873761587</v>
       </c>
       <c r="E96">
-        <v>353.6100000000001</v>
+        <v>361.2250000000001</v>
       </c>
       <c r="F96">
-        <v>715.8100000000001</v>
+        <v>723.4250000000001</v>
       </c>
       <c r="G96">
         <v>14.2</v>
@@ -9159,37 +9159,37 @@
         <v>26.425</v>
       </c>
       <c r="M96">
-        <v>168.787998</v>
+        <v>170.583615</v>
       </c>
       <c r="N96">
-        <v>-142.362998</v>
+        <v>-144.158615</v>
       </c>
       <c r="O96">
-        <v>-28.4725996</v>
+        <v>-28.831723</v>
       </c>
       <c r="P96">
-        <v>-113.8903984</v>
+        <v>-115.326892</v>
       </c>
       <c r="Q96">
-        <v>-66.69039840000001</v>
+        <v>-68.126892</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.507534748539709</v>
+        <v>0.599881698247651</v>
       </c>
       <c r="T96">
-        <v>8.75893755825285</v>
+        <v>10.51072506990342</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03131146801089494</v>
+        <v>0.03098187361078026</v>
       </c>
       <c r="W96">
-        <v>0.228416755843031</v>
+        <v>0.228494474202578</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1565573400544747</v>
+        <v>0.1549093680539013</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2470638354048316</v>
+        <v>0.2489638354048317</v>
       </c>
       <c r="C97">
-        <v>-602.9734126238413</v>
+        <v>-611.5696788661348</v>
       </c>
       <c r="D97">
-        <v>106.2515873761587</v>
+        <v>105.2703211338653</v>
       </c>
       <c r="E97">
-        <v>361.2250000000001</v>
+        <v>368.8400000000001</v>
       </c>
       <c r="F97">
-        <v>723.4250000000001</v>
+        <v>731.0400000000001</v>
       </c>
       <c r="G97">
         <v>14.2</v>
@@ -9241,37 +9241,37 @@
         <v>26.425</v>
       </c>
       <c r="M97">
-        <v>170.583615</v>
+        <v>172.379232</v>
       </c>
       <c r="N97">
-        <v>-144.158615</v>
+        <v>-145.954232</v>
       </c>
       <c r="O97">
-        <v>-28.831723</v>
+        <v>-29.19084640000001</v>
       </c>
       <c r="P97">
-        <v>-115.326892</v>
+        <v>-116.7633856</v>
       </c>
       <c r="Q97">
-        <v>-68.126892</v>
+        <v>-69.56338560000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.599881698247651</v>
+        <v>0.7384021228095642</v>
       </c>
       <c r="T97">
-        <v>10.51072506990342</v>
+        <v>13.13840633737929</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03098187361078026</v>
+        <v>0.03065914576066796</v>
       </c>
       <c r="W97">
-        <v>0.228494474202578</v>
+        <v>0.2285705734296345</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1549093680539013</v>
+        <v>0.1532957288033397</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2489638354048316</v>
+        <v>0.2508638354048316</v>
       </c>
       <c r="C98">
-        <v>-611.5696788661345</v>
+        <v>-620.1479863689974</v>
       </c>
       <c r="D98">
-        <v>105.2703211338654</v>
+        <v>104.3070136310026</v>
       </c>
       <c r="E98">
-        <v>368.84</v>
+        <v>376.455</v>
       </c>
       <c r="F98">
-        <v>731.04</v>
+        <v>738.655</v>
       </c>
       <c r="G98">
         <v>14.2</v>
@@ -9323,37 +9323,37 @@
         <v>26.425</v>
       </c>
       <c r="M98">
-        <v>172.379232</v>
+        <v>174.174849</v>
       </c>
       <c r="N98">
-        <v>-145.954232</v>
+        <v>-147.749849</v>
       </c>
       <c r="O98">
-        <v>-29.1908464</v>
+        <v>-29.5499698</v>
       </c>
       <c r="P98">
-        <v>-116.7633856</v>
+        <v>-118.1998792</v>
       </c>
       <c r="Q98">
-        <v>-69.56338559999999</v>
+        <v>-70.99987919999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7384021228095622</v>
+        <v>0.9692694970794163</v>
       </c>
       <c r="T98">
-        <v>13.13840633737925</v>
+        <v>17.51787511650567</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03065914576066797</v>
+        <v>0.03034307209303222</v>
       </c>
       <c r="W98">
-        <v>0.2285705734296345</v>
+        <v>0.228645103600463</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1532957288033399</v>
+        <v>0.1517153604651611</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2508638354048316</v>
+        <v>0.2527638354048316</v>
       </c>
       <c r="C99">
-        <v>-620.1479863689974</v>
+        <v>-628.7088236723201</v>
       </c>
       <c r="D99">
-        <v>104.3070136310026</v>
+        <v>103.3611763276799</v>
       </c>
       <c r="E99">
-        <v>376.455</v>
+        <v>384.07</v>
       </c>
       <c r="F99">
-        <v>738.655</v>
+        <v>746.27</v>
       </c>
       <c r="G99">
         <v>14.2</v>
@@ -9405,37 +9405,37 @@
         <v>26.425</v>
       </c>
       <c r="M99">
-        <v>174.174849</v>
+        <v>175.970466</v>
       </c>
       <c r="N99">
-        <v>-147.749849</v>
+        <v>-149.545466</v>
       </c>
       <c r="O99">
-        <v>-29.5499698</v>
+        <v>-29.90909320000001</v>
       </c>
       <c r="P99">
-        <v>-118.1998792</v>
+        <v>-119.6363728</v>
       </c>
       <c r="Q99">
-        <v>-70.99987919999998</v>
+        <v>-72.43637280000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9692694970794163</v>
+        <v>1.431004245619125</v>
       </c>
       <c r="T99">
-        <v>17.51787511650567</v>
+        <v>26.2768126747585</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03034307209303222</v>
+        <v>0.03003344890840944</v>
       </c>
       <c r="W99">
-        <v>0.228645103600463</v>
+        <v>0.2287181127473971</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1517153604651611</v>
+        <v>0.1501672445420471</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2527638354048316</v>
+        <v>0.2546638354048317</v>
       </c>
       <c r="C100">
-        <v>-628.7088236723201</v>
+        <v>-637.2526617552624</v>
       </c>
       <c r="D100">
-        <v>103.3611763276799</v>
+        <v>102.4323382447377</v>
       </c>
       <c r="E100">
-        <v>384.07</v>
+        <v>391.685</v>
       </c>
       <c r="F100">
-        <v>746.27</v>
+        <v>753.885</v>
       </c>
       <c r="G100">
         <v>14.2</v>
@@ -9487,37 +9487,37 @@
         <v>26.425</v>
       </c>
       <c r="M100">
-        <v>175.970466</v>
+        <v>177.766083</v>
       </c>
       <c r="N100">
-        <v>-149.545466</v>
+        <v>-151.341083</v>
       </c>
       <c r="O100">
-        <v>-29.90909320000001</v>
+        <v>-30.26821660000001</v>
       </c>
       <c r="P100">
-        <v>-119.6363728</v>
+        <v>-121.0728664</v>
       </c>
       <c r="Q100">
-        <v>-72.43637280000003</v>
+        <v>-73.87286640000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.431004245619125</v>
+        <v>2.816208491238249</v>
       </c>
       <c r="T100">
-        <v>26.2768126747585</v>
+        <v>52.553625349517</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03003344890840944</v>
+        <v>0.02973008073761742</v>
       </c>
       <c r="W100">
-        <v>0.2287181127473971</v>
+        <v>0.2287896469620698</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1501672445420471</v>
+        <v>0.148650403688087</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2546638354048317</v>
-      </c>
-      <c r="C101">
-        <v>-637.2526617552624</v>
-      </c>
-      <c r="D101">
-        <v>102.4323382447377</v>
-      </c>
-      <c r="E101">
-        <v>391.685</v>
-      </c>
-      <c r="F101">
-        <v>753.885</v>
-      </c>
-      <c r="G101">
-        <v>14.2</v>
-      </c>
-      <c r="H101">
-        <v>399.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>73.625</v>
-      </c>
-      <c r="K101">
-        <v>47.2</v>
-      </c>
-      <c r="L101">
-        <v>26.425</v>
-      </c>
-      <c r="M101">
-        <v>177.766083</v>
-      </c>
-      <c r="N101">
-        <v>-151.341083</v>
-      </c>
-      <c r="O101">
-        <v>-30.26821660000001</v>
-      </c>
-      <c r="P101">
-        <v>-121.0728664</v>
-      </c>
-      <c r="Q101">
-        <v>-73.87286640000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.816208491238249</v>
-      </c>
-      <c r="T101">
-        <v>52.553625349517</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02973008073761742</v>
-      </c>
-      <c r="W101">
-        <v>0.2287896469620698</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.148650403688087</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
